--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model_info[生物模型详情信息] .xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model_info[生物模型详情信息] .xlsx
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G441"/>
+  <dimension ref="A1:G443"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="3" min="1" max="1"/>
@@ -3539,24 +3539,24 @@
       </c>
     </row>
     <row r="101" s="3">
-      <c r="A101" s="2" t="n">
-        <v>1910001</v>
-      </c>
-      <c r="B101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Weapon/Weapon_R_1</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="A101" t="n">
+        <v>1900015</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>90</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Weapon/Weapon_L_15</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>人类-武器</t>
         </is>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="102" s="3">
       <c r="A102" s="2" t="n">
-        <v>1910002</v>
+        <v>1910001</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>1</v>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_2</t>
+          <t>Weapon/Weapon_R_1</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -3588,7 +3588,7 @@
     </row>
     <row r="103" s="3">
       <c r="A103" s="2" t="n">
-        <v>1910003</v>
+        <v>1910002</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>1</v>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_3</t>
+          <t>Weapon/Weapon_R_2</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
     </row>
     <row r="104" s="3">
       <c r="A104" s="2" t="n">
-        <v>1920021</v>
+        <v>1910003</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>1</v>
@@ -3621,11 +3621,11 @@
         <v>0</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_LR_21</t>
+          <t>Weapon/Weapon_R_3</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1920022</v>
+        <v>1920021</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>1</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_LR_22</t>
+          <t>Weapon/Weapon_LR_21</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -3660,50 +3660,55 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>2000001</v>
+        <v>1920022</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Base/Base_1</t>
+          <t>Weapon/Weapon_LR_22</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>骷髅-基础</t>
+          <t>人类-武器</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>2010000</v>
+        <v>1920014</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1</v>
+        <v>92</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Weapon/Weapon_LR_14</t>
+        </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>骷髅-头</t>
+          <t>人类-武器</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>2010001</v>
+        <v>2000001</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>2</v>
@@ -3712,22 +3717,22 @@
         <v>0</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_1</t>
+          <t>Base/Base_1</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>骷髅-头</t>
+          <t>骷髅-基础</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>2010002</v>
+        <v>2010000</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>2</v>
@@ -3738,11 +3743,6 @@
       <c r="D109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>Head/Head_2</t>
-        </is>
-      </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
           <t>骷髅-头</t>
@@ -3751,7 +3751,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>2010003</v>
+        <v>2010001</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>2</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_3</t>
+          <t>Head/Head_1</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>2010004</v>
+        <v>2010002</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>2</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_4</t>
+          <t>Head/Head_2</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>2010005</v>
+        <v>2010003</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>2</v>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_5</t>
+          <t>Head/Head_3</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>2010006</v>
+        <v>2010004</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>2</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_6</t>
+          <t>Head/Head_4</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -3847,7 +3847,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>2010007</v>
+        <v>2010005</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>2</v>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_7</t>
+          <t>Head/Head_5</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>2010008</v>
+        <v>2010006</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>2</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_8</t>
+          <t>Head/Head_6</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>2010009</v>
+        <v>2010007</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>2</v>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_9</t>
+          <t>Head/Head_7</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>2010010</v>
+        <v>2010008</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>2</v>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_10</t>
+          <t>Head/Head_8</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>2010011</v>
+        <v>2010009</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>2</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_11</t>
+          <t>Head/Head_9</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>2010012</v>
+        <v>2010010</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>2</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_12</t>
+          <t>Head/Head_10</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>2010013</v>
+        <v>2010011</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>2</v>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Head/Head_13</t>
+          <t>Head/Head_11</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>2500001</v>
+        <v>2010012</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>2</v>
@@ -4024,22 +4024,22 @@
         <v>0</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_1</t>
+          <t>Head/Head_12</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>骷髅-帽子-皇冠</t>
+          <t>骷髅-头</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>2500002</v>
+        <v>2010013</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>2</v>
@@ -4048,22 +4048,22 @@
         <v>0</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_2</t>
+          <t>Head/Head_13</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>骷髅-帽子-铁制头盔</t>
+          <t>骷髅-头</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>2500003</v>
+        <v>2500001</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>2</v>
@@ -4076,18 +4076,18 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_3</t>
+          <t>Hat/Hat_1</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>骷髅-帽子-异域头巾</t>
+          <t>骷髅-帽子-皇冠</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>2500004</v>
+        <v>2500002</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>2</v>
@@ -4100,18 +4100,18 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_4</t>
+          <t>Hat/Hat_2</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>骷髅-帽子-魔力帽</t>
+          <t>骷髅-帽子-铁制头盔</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>2500005</v>
+        <v>2500003</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>2</v>
@@ -4124,18 +4124,18 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_5</t>
+          <t>Hat/Hat_3</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>骷髅-帽子-草帽</t>
+          <t>骷髅-帽子-异域头巾</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>2500006</v>
+        <v>2500004</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>2</v>
@@ -4148,18 +4148,18 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_6</t>
+          <t>Hat/Hat_4</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>骷髅-帽子-恶魔头颅</t>
+          <t>骷髅-帽子-魔力帽</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>2500007</v>
+        <v>2500005</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>2</v>
@@ -4172,18 +4172,18 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_7</t>
+          <t>Hat/Hat_5</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>骷髅-帽子-魔王之角</t>
+          <t>骷髅-帽子-草帽</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>2510001</v>
+        <v>2500006</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>2</v>
@@ -4192,22 +4192,22 @@
         <v>0</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_1</t>
+          <t>Hat/Hat_6</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-质朴肩甲</t>
+          <t>骷髅-帽子-恶魔头颅</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>2510002</v>
+        <v>2500007</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>2</v>
@@ -4216,22 +4216,22 @@
         <v>0</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_2</t>
+          <t>Hat/Hat_7</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-加长肩甲</t>
+          <t>骷髅-帽子-魔王之角</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>2510003</v>
+        <v>2510001</v>
       </c>
       <c r="B130" s="2" t="n">
         <v>2</v>
@@ -4244,18 +4244,18 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_3</t>
+          <t>Clothes/Clothes_1</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-破烂肩甲</t>
+          <t>骷髅-衣服-质朴肩甲</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>2510004</v>
+        <v>2510002</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>2</v>
@@ -4268,18 +4268,18 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_4</t>
+          <t>Clothes/Clothes_2</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-丝绸披肩</t>
+          <t>骷髅-衣服-加长肩甲</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>2510005</v>
+        <v>2510003</v>
       </c>
       <c r="B132" s="2" t="n">
         <v>2</v>
@@ -4292,18 +4292,18 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_5</t>
+          <t>Clothes/Clothes_3</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-魔法披肩</t>
+          <t>骷髅-衣服-破烂肩甲</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>2510006</v>
+        <v>2510004</v>
       </c>
       <c r="B133" s="2" t="n">
         <v>2</v>
@@ -4316,18 +4316,18 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_6</t>
+          <t>Clothes/Clothes_4</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-麻布衣</t>
+          <t>骷髅-衣服-丝绸披肩</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>2510007</v>
+        <v>2510005</v>
       </c>
       <c r="B134" s="2" t="n">
         <v>2</v>
@@ -4340,18 +4340,18 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_7</t>
+          <t>Clothes/Clothes_5</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-蔚蓝铠甲</t>
+          <t>骷髅-衣服-魔法披肩</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>2510008</v>
+        <v>2510006</v>
       </c>
       <c r="B135" s="2" t="n">
         <v>2</v>
@@ -4364,18 +4364,18 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_8</t>
+          <t>Clothes/Clothes_6</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-破烂法衣</t>
+          <t>骷髅-衣服-麻布衣</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>2510009</v>
+        <v>2510007</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>2</v>
@@ -4388,18 +4388,18 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_9</t>
+          <t>Clothes/Clothes_7</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-琥珀铠甲</t>
+          <t>骷髅-衣服-蔚蓝铠甲</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>2510010</v>
+        <v>2510008</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>2</v>
@@ -4412,18 +4412,18 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_10</t>
+          <t>Clothes/Clothes_8</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-远古铠甲</t>
+          <t>骷髅-衣服-破烂法衣</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>2510011</v>
+        <v>2510009</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>2</v>
@@ -4436,18 +4436,18 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_11</t>
+          <t>Clothes/Clothes_9</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>骷髅-衣服-深红战衣</t>
+          <t>骷髅-衣服-琥珀铠甲</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>2520001</v>
+        <v>2510010</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>2</v>
@@ -4456,22 +4456,22 @@
         <v>0</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_1</t>
+          <t>Clothes/Clothes_10</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>骷髅-裤子-破烂腰带</t>
+          <t>骷髅-衣服-远古铠甲</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>2520003</v>
+        <v>2510011</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>2</v>
@@ -4480,22 +4480,22 @@
         <v>0</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_3</t>
+          <t>Clothes/Clothes_11</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>骷髅-裤子-破烂法裤</t>
+          <t>骷髅-衣服-深红战衣</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>2520007</v>
+        <v>2520001</v>
       </c>
       <c r="B141" s="2" t="n">
         <v>2</v>
@@ -4508,18 +4508,18 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_7</t>
+          <t>Pants/Pants_1</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>骷髅-裤子-蔚蓝腰带</t>
+          <t>骷髅-裤子-破烂腰带</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>2520009</v>
+        <v>2520003</v>
       </c>
       <c r="B142" s="2" t="n">
         <v>2</v>
@@ -4532,18 +4532,18 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_9</t>
+          <t>Pants/Pants_3</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>骷髅-裤子-琥珀腰带</t>
+          <t>骷髅-裤子-破烂法裤</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>2520011</v>
+        <v>2520007</v>
       </c>
       <c r="B143" s="2" t="n">
         <v>2</v>
@@ -4556,18 +4556,18 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_11</t>
+          <t>Pants/Pants_7</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>骷髅-裤子-深红腰带</t>
+          <t>骷髅-裤子-蔚蓝腰带</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>2900001</v>
+        <v>2520009</v>
       </c>
       <c r="B144" s="2" t="n">
         <v>2</v>
@@ -4576,22 +4576,22 @@
         <v>0</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_1</t>
+          <t>Pants/Pants_9</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-骨头</t>
+          <t>骷髅-裤子-琥珀腰带</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>2900002</v>
+        <v>2520011</v>
       </c>
       <c r="B145" s="2" t="n">
         <v>2</v>
@@ -4600,22 +4600,22 @@
         <v>0</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_2</t>
+          <t>Pants/Pants_11</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-鸡腿</t>
+          <t>骷髅-裤子-深红腰带</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>2900003</v>
+        <v>2900001</v>
       </c>
       <c r="B146" s="2" t="n">
         <v>2</v>
@@ -4628,18 +4628,18 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_3</t>
+          <t>Weapon/Weapon_L_1</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-无用之书</t>
+          <t>骷髅-武器-骨头</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>2900004</v>
+        <v>2900002</v>
       </c>
       <c r="B147" s="2" t="n">
         <v>2</v>
@@ -4652,18 +4652,18 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_4</t>
+          <t>Weapon/Weapon_L_2</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-木制圆盾</t>
+          <t>骷髅-武器-鸡腿</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>2900005</v>
+        <v>2900003</v>
       </c>
       <c r="B148" s="2" t="n">
         <v>2</v>
@@ -4676,18 +4676,18 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_5</t>
+          <t>Weapon/Weapon_L_3</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-飞镖</t>
+          <t>骷髅-武器-无用之书</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>2900006</v>
+        <v>2900004</v>
       </c>
       <c r="B149" s="2" t="n">
         <v>2</v>
@@ -4700,18 +4700,18 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_6</t>
+          <t>Weapon/Weapon_L_4</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-骷髅头</t>
+          <t>骷髅-武器-木制圆盾</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>2900007</v>
+        <v>2900005</v>
       </c>
       <c r="B150" s="2" t="n">
         <v>2</v>
@@ -4724,18 +4724,18 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_7</t>
+          <t>Weapon/Weapon_L_5</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-欧里给</t>
+          <t>骷髅-武器-飞镖</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>2900008</v>
+        <v>2900006</v>
       </c>
       <c r="B151" s="2" t="n">
         <v>2</v>
@@ -4748,18 +4748,18 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_8</t>
+          <t>Weapon/Weapon_L_6</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-苹果</t>
+          <t>骷髅-武器-骷髅头</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>2900009</v>
+        <v>2900007</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>2</v>
@@ -4772,18 +4772,18 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_9</t>
+          <t>Weapon/Weapon_L_7</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-28年拉菲</t>
+          <t>骷髅-武器-欧里给</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>2900010</v>
+        <v>2900008</v>
       </c>
       <c r="B153" s="2" t="n">
         <v>2</v>
@@ -4796,18 +4796,18 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_10</t>
+          <t>Weapon/Weapon_L_8</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-金币</t>
+          <t>骷髅-武器-苹果</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>2910001</v>
+        <v>2900009</v>
       </c>
       <c r="B154" s="2" t="n">
         <v>2</v>
@@ -4816,22 +4816,22 @@
         <v>0</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_1</t>
+          <t>Weapon/Weapon_L_9</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-铁剑</t>
+          <t>骷髅-武器-28年拉菲</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>2910002</v>
+        <v>2900010</v>
       </c>
       <c r="B155" s="2" t="n">
         <v>2</v>
@@ -4840,22 +4840,22 @@
         <v>0</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_2</t>
+          <t>Weapon/Weapon_L_10</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-火法杖</t>
+          <t>骷髅-武器-金币</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>2910003</v>
+        <v>2910001</v>
       </c>
       <c r="B156" s="2" t="n">
         <v>2</v>
@@ -4868,18 +4868,18 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_3</t>
+          <t>Weapon/Weapon_R_1</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-冰法杖</t>
+          <t>骷髅-武器-铁剑</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>2910004</v>
+        <v>2910002</v>
       </c>
       <c r="B157" s="2" t="n">
         <v>2</v>
@@ -4892,18 +4892,18 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_4</t>
+          <t>Weapon/Weapon_R_2</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-残破剑</t>
+          <t>骷髅-武器-火法杖</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>2910005</v>
+        <v>2910003</v>
       </c>
       <c r="B158" s="2" t="n">
         <v>2</v>
@@ -4916,18 +4916,18 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_5</t>
+          <t>Weapon/Weapon_R_3</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-波斯短刀</t>
+          <t>骷髅-武器-冰法杖</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>2910006</v>
+        <v>2910004</v>
       </c>
       <c r="B159" s="2" t="n">
         <v>2</v>
@@ -4940,18 +4940,18 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_6</t>
+          <t>Weapon/Weapon_R_4</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-骷髅剑</t>
+          <t>骷髅-武器-残破剑</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>2910007</v>
+        <v>2910005</v>
       </c>
       <c r="B160" s="2" t="n">
         <v>2</v>
@@ -4964,18 +4964,18 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_7</t>
+          <t>Weapon/Weapon_R_5</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-金色刺剑</t>
+          <t>骷髅-武器-波斯短刀</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>2910008</v>
+        <v>2910006</v>
       </c>
       <c r="B161" s="2" t="n">
         <v>2</v>
@@ -4988,18 +4988,18 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_8</t>
+          <t>Weapon/Weapon_R_6</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-铲子</t>
+          <t>骷髅-武器-骷髅剑</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>2910009</v>
+        <v>2910007</v>
       </c>
       <c r="B162" s="2" t="n">
         <v>2</v>
@@ -5012,18 +5012,18 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_9</t>
+          <t>Weapon/Weapon_R_7</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-冰之哀伤</t>
+          <t>骷髅-武器-金色刺剑</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>2910010</v>
+        <v>2910008</v>
       </c>
       <c r="B163" s="2" t="n">
         <v>2</v>
@@ -5036,18 +5036,18 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_10</t>
+          <t>Weapon/Weapon_R_8</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-火之高兴</t>
+          <t>骷髅-武器-铲子</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>2910011</v>
+        <v>2910009</v>
       </c>
       <c r="B164" s="2" t="n">
         <v>2</v>
@@ -5060,18 +5060,18 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_11</t>
+          <t>Weapon/Weapon_R_9</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-绿宝石法杖</t>
+          <t>骷髅-武器-冰之哀伤</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>2910012</v>
+        <v>2910010</v>
       </c>
       <c r="B165" s="2" t="n">
         <v>2</v>
@@ -5084,18 +5084,18 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_12</t>
+          <t>Weapon/Weapon_R_10</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-魔力法杖</t>
+          <t>骷髅-武器-火之高兴</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>2910013</v>
+        <v>2910011</v>
       </c>
       <c r="B166" s="2" t="n">
         <v>2</v>
@@ -5108,18 +5108,18 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_13</t>
+          <t>Weapon/Weapon_R_11</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-扫帚</t>
+          <t>骷髅-武器-绿宝石法杖</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>2910014</v>
+        <v>2910012</v>
       </c>
       <c r="B167" s="2" t="n">
         <v>2</v>
@@ -5132,18 +5132,18 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_14</t>
+          <t>Weapon/Weapon_R_12</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-星之法杖</t>
+          <t>骷髅-武器-魔力法杖</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>2910015</v>
+        <v>2910013</v>
       </c>
       <c r="B168" s="2" t="n">
         <v>2</v>
@@ -5156,18 +5156,18 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_15</t>
+          <t>Weapon/Weapon_R_13</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-百变法杖</t>
+          <t>骷髅-武器-扫帚</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>2910016</v>
+        <v>2910014</v>
       </c>
       <c r="B169" s="2" t="n">
         <v>2</v>
@@ -5180,18 +5180,18 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_16</t>
+          <t>Weapon/Weapon_R_14</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-琥珀法杖</t>
+          <t>骷髅-武器-星之法杖</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>2910017</v>
+        <v>2910015</v>
       </c>
       <c r="B170" s="2" t="n">
         <v>2</v>
@@ -5204,18 +5204,18 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_17</t>
+          <t>Weapon/Weapon_R_15</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-爱之天使</t>
+          <t>骷髅-武器-百变法杖</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>2910018</v>
+        <v>2910016</v>
       </c>
       <c r="B171" s="2" t="n">
         <v>2</v>
@@ -5228,18 +5228,18 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_18</t>
+          <t>Weapon/Weapon_R_16</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-星域之杖</t>
+          <t>骷髅-武器-琥珀法杖</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>2910019</v>
+        <v>2910017</v>
       </c>
       <c r="B172" s="2" t="n">
         <v>2</v>
@@ -5252,18 +5252,18 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_19</t>
+          <t>Weapon/Weapon_R_17</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-结晶法杖</t>
+          <t>骷髅-武器-爱之天使</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>2910020</v>
+        <v>2910018</v>
       </c>
       <c r="B173" s="2" t="n">
         <v>2</v>
@@ -5276,69 +5276,66 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_20</t>
+          <t>Weapon/Weapon_R_18</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>骷髅-武器-黑暗法杖</t>
+          <t>骷髅-武器-星域之杖</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>3040001</v>
+        <v>2910019</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C174" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Body/Body_1</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="n">
-        <v>1</v>
+          <t>Weapon/Weapon_R_19</t>
+        </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-身体-1</t>
+          <t>骷髅-武器-结晶法杖</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>3050001</v>
+        <v>2910020</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C175" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_1</t>
+          <t>Weapon/Weapon_R_20</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-眼睛-1</t>
+          <t>骷髅-武器-黑暗法杖</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>3050002</v>
+        <v>3040001</v>
       </c>
       <c r="B176" s="2" t="n">
         <v>3</v>
@@ -5347,22 +5344,25 @@
         <v>0</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_2</t>
-        </is>
+          <t>Body/Body_1</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-眼睛-2</t>
+          <t>史莱姆-身体-1</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>3050003</v>
+        <v>3050001</v>
       </c>
       <c r="B177" s="2" t="n">
         <v>3</v>
@@ -5375,18 +5375,18 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_3</t>
+          <t>Eye/Eye_1</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-眼睛-3</t>
+          <t>史莱姆-眼睛-1</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>3050004</v>
+        <v>3050002</v>
       </c>
       <c r="B178" s="2" t="n">
         <v>3</v>
@@ -5399,18 +5399,18 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_4</t>
+          <t>Eye/Eye_2</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-眼睛-4</t>
+          <t>史莱姆-眼睛-2</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>3050005</v>
+        <v>3050003</v>
       </c>
       <c r="B179" s="2" t="n">
         <v>3</v>
@@ -5423,18 +5423,18 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_5</t>
+          <t>Eye/Eye_3</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-眼睛-5</t>
+          <t>史莱姆-眼睛-3</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>3050006</v>
+        <v>3050004</v>
       </c>
       <c r="B180" s="2" t="n">
         <v>3</v>
@@ -5447,18 +5447,18 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_6</t>
+          <t>Eye/Eye_4</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-眼睛-6</t>
+          <t>史莱姆-眼睛-4</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>3050007</v>
+        <v>3050005</v>
       </c>
       <c r="B181" s="2" t="n">
         <v>3</v>
@@ -5471,18 +5471,18 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_7</t>
+          <t>Eye/Eye_5</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-眼睛-7</t>
+          <t>史莱姆-眼睛-5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>3050008</v>
+        <v>3050006</v>
       </c>
       <c r="B182" s="2" t="n">
         <v>3</v>
@@ -5495,18 +5495,18 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_8</t>
+          <t>Eye/Eye_6</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-眼睛-8</t>
+          <t>史莱姆-眼睛-6</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>3050009</v>
+        <v>3050007</v>
       </c>
       <c r="B183" s="2" t="n">
         <v>3</v>
@@ -5519,18 +5519,18 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_9</t>
+          <t>Eye/Eye_7</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-眼睛-9</t>
+          <t>史莱姆-眼睛-7</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>3050010</v>
+        <v>3050008</v>
       </c>
       <c r="B184" s="2" t="n">
         <v>3</v>
@@ -5543,18 +5543,18 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_10</t>
+          <t>Eye/Eye_8</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-眼睛-10</t>
+          <t>史莱姆-眼睛-8</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>3020001</v>
+        <v>3050009</v>
       </c>
       <c r="B185" s="2" t="n">
         <v>3</v>
@@ -5563,22 +5563,22 @@
         <v>0</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_1</t>
+          <t>Eye/Eye_9</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-1</t>
+          <t>史莱姆-眼睛-9</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>3020002</v>
+        <v>3050010</v>
       </c>
       <c r="B186" s="2" t="n">
         <v>3</v>
@@ -5587,22 +5587,22 @@
         <v>0</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_2</t>
+          <t>Eye/Eye_10</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-2</t>
+          <t>史莱姆-眼睛-10</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>3020003</v>
+        <v>3020001</v>
       </c>
       <c r="B187" s="2" t="n">
         <v>3</v>
@@ -5615,18 +5615,18 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_3</t>
+          <t>Hat/Hat_1</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-3</t>
+          <t>史莱姆-帽子-1</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>3020004</v>
+        <v>3020002</v>
       </c>
       <c r="B188" s="2" t="n">
         <v>3</v>
@@ -5639,18 +5639,18 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_4</t>
+          <t>Hat/Hat_2</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-4</t>
+          <t>史莱姆-帽子-2</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>3020005</v>
+        <v>3020003</v>
       </c>
       <c r="B189" s="2" t="n">
         <v>3</v>
@@ -5663,18 +5663,18 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_5</t>
+          <t>Hat/Hat_3</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-5</t>
+          <t>史莱姆-帽子-3</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>3020006</v>
+        <v>3020004</v>
       </c>
       <c r="B190" s="2" t="n">
         <v>3</v>
@@ -5687,18 +5687,18 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_6</t>
+          <t>Hat/Hat_4</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-6</t>
+          <t>史莱姆-帽子-4</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>3020007</v>
+        <v>3020005</v>
       </c>
       <c r="B191" s="2" t="n">
         <v>3</v>
@@ -5711,18 +5711,18 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_7</t>
+          <t>Hat/Hat_5</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-7</t>
+          <t>史莱姆-帽子-5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>3020008</v>
+        <v>3020006</v>
       </c>
       <c r="B192" s="2" t="n">
         <v>3</v>
@@ -5735,18 +5735,18 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_8</t>
+          <t>Hat/Hat_6</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-8</t>
+          <t>史莱姆-帽子-6</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>3020009</v>
+        <v>3020007</v>
       </c>
       <c r="B193" s="2" t="n">
         <v>3</v>
@@ -5759,18 +5759,18 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_9</t>
+          <t>Hat/Hat_7</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-9</t>
+          <t>史莱姆-帽子-7</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>3020010</v>
+        <v>3020008</v>
       </c>
       <c r="B194" s="2" t="n">
         <v>3</v>
@@ -5783,18 +5783,18 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_10</t>
+          <t>Hat/Hat_8</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-10</t>
+          <t>史莱姆-帽子-8</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>3020011</v>
+        <v>3020009</v>
       </c>
       <c r="B195" s="2" t="n">
         <v>3</v>
@@ -5807,18 +5807,18 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_11</t>
+          <t>Hat/Hat_9</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-11</t>
+          <t>史莱姆-帽子-9</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>3020012</v>
+        <v>3020010</v>
       </c>
       <c r="B196" s="2" t="n">
         <v>3</v>
@@ -5831,18 +5831,18 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_12</t>
+          <t>Hat/Hat_10</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-12</t>
+          <t>史莱姆-帽子-10</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>3020013</v>
+        <v>3020011</v>
       </c>
       <c r="B197" s="2" t="n">
         <v>3</v>
@@ -5855,18 +5855,18 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_13</t>
+          <t>Hat/Hat_11</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-13</t>
+          <t>史莱姆-帽子-11</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>3020014</v>
+        <v>3020012</v>
       </c>
       <c r="B198" s="2" t="n">
         <v>3</v>
@@ -5879,18 +5879,18 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_14</t>
+          <t>Hat/Hat_12</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-14</t>
+          <t>史莱姆-帽子-12</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>3020015</v>
+        <v>3020013</v>
       </c>
       <c r="B199" s="2" t="n">
         <v>3</v>
@@ -5903,18 +5903,18 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_15</t>
+          <t>Hat/Hat_13</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-15</t>
+          <t>史莱姆-帽子-13</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>3020016</v>
+        <v>3020014</v>
       </c>
       <c r="B200" s="2" t="n">
         <v>3</v>
@@ -5927,18 +5927,18 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_16</t>
+          <t>Hat/Hat_14</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-16</t>
+          <t>史莱姆-帽子-14</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>3020017</v>
+        <v>3020015</v>
       </c>
       <c r="B201" s="2" t="n">
         <v>3</v>
@@ -5951,18 +5951,18 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_17</t>
+          <t>Hat/Hat_15</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-17</t>
+          <t>史莱姆-帽子-15</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>3020018</v>
+        <v>3020016</v>
       </c>
       <c r="B202" s="2" t="n">
         <v>3</v>
@@ -5975,18 +5975,18 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_18</t>
+          <t>Hat/Hat_16</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-18</t>
+          <t>史莱姆-帽子-16</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>3020019</v>
+        <v>3020017</v>
       </c>
       <c r="B203" s="2" t="n">
         <v>3</v>
@@ -5999,18 +5999,18 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_19</t>
+          <t>Hat/Hat_17</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-19</t>
+          <t>史莱姆-帽子-17</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>3020020</v>
+        <v>3020018</v>
       </c>
       <c r="B204" s="2" t="n">
         <v>3</v>
@@ -6023,66 +6023,66 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_20</t>
+          <t>Hat/Hat_18</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>史莱姆-帽子-20</t>
+          <t>史莱姆-帽子-18</t>
         </is>
       </c>
     </row>
     <row r="205" s="3">
       <c r="A205" s="2" t="n">
-        <v>4000001</v>
+        <v>3020019</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C205" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Base/Base_1</t>
+          <t>Hat/Hat_19</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>基础1</t>
+          <t>史莱姆-帽子-19</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>4030001</v>
+        <v>3020020</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C206" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_1</t>
+          <t>Hat/Hat_20</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>发型1</t>
+          <t>史莱姆-帽子-20</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>4030002</v>
+        <v>4000001</v>
       </c>
       <c r="B207" s="2" t="n">
         <v>4</v>
@@ -6091,22 +6091,22 @@
         <v>0</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_2</t>
+          <t>Base/Base_1</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>发型2</t>
+          <t>基础1</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>4030003</v>
+        <v>4030001</v>
       </c>
       <c r="B208" s="2" t="n">
         <v>4</v>
@@ -6119,18 +6119,18 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_3</t>
+          <t>Hair/Hair_1</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>发型3</t>
+          <t>发型1</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>4030004</v>
+        <v>4030002</v>
       </c>
       <c r="B209" s="2" t="n">
         <v>4</v>
@@ -6143,18 +6143,18 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_4</t>
+          <t>Hair/Hair_2</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>发型4</t>
+          <t>发型2</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>4030005</v>
+        <v>4030003</v>
       </c>
       <c r="B210" s="2" t="n">
         <v>4</v>
@@ -6167,18 +6167,18 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_5</t>
+          <t>Hair/Hair_3</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>发型5</t>
+          <t>发型3</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>4030006</v>
+        <v>4030004</v>
       </c>
       <c r="B211" s="2" t="n">
         <v>4</v>
@@ -6191,18 +6191,18 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_6</t>
+          <t>Hair/Hair_4</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>发型6</t>
+          <t>发型4</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>4030007</v>
+        <v>4030005</v>
       </c>
       <c r="B212" s="2" t="n">
         <v>4</v>
@@ -6215,18 +6215,18 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_7</t>
+          <t>Hair/Hair_5</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>发型7</t>
+          <t>发型5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>4030008</v>
+        <v>4030006</v>
       </c>
       <c r="B213" s="2" t="n">
         <v>4</v>
@@ -6239,18 +6239,18 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_8</t>
+          <t>Hair/Hair_6</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>发型8</t>
+          <t>发型6</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>4030009</v>
+        <v>4030007</v>
       </c>
       <c r="B214" s="2" t="n">
         <v>4</v>
@@ -6263,18 +6263,18 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_9</t>
+          <t>Hair/Hair_7</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>发型9</t>
+          <t>发型7</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>4030010</v>
+        <v>4030008</v>
       </c>
       <c r="B215" s="2" t="n">
         <v>4</v>
@@ -6287,18 +6287,18 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_10</t>
+          <t>Hair/Hair_8</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>发型10</t>
+          <t>发型8</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>4050001</v>
+        <v>4030009</v>
       </c>
       <c r="B216" s="2" t="n">
         <v>4</v>
@@ -6307,22 +6307,22 @@
         <v>0</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_1</t>
+          <t>Hair/Hair_9</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>眼睛-1</t>
+          <t>发型9</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>4050002</v>
+        <v>4030010</v>
       </c>
       <c r="B217" s="2" t="n">
         <v>4</v>
@@ -6331,22 +6331,22 @@
         <v>0</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_2</t>
+          <t>Hair/Hair_10</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>眼睛-2</t>
+          <t>发型10</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>4050003</v>
+        <v>4050001</v>
       </c>
       <c r="B218" s="2" t="n">
         <v>4</v>
@@ -6359,18 +6359,18 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_3</t>
+          <t>Eye/Eye_1</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>眼睛-3</t>
+          <t>眼睛-1</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>4050004</v>
+        <v>4050002</v>
       </c>
       <c r="B219" s="2" t="n">
         <v>4</v>
@@ -6383,18 +6383,18 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_4</t>
+          <t>Eye/Eye_2</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>眼睛-4</t>
+          <t>眼睛-2</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>4050005</v>
+        <v>4050003</v>
       </c>
       <c r="B220" s="2" t="n">
         <v>4</v>
@@ -6407,18 +6407,18 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_5</t>
+          <t>Eye/Eye_3</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>眼睛-5</t>
+          <t>眼睛-3</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>4050006</v>
+        <v>4050004</v>
       </c>
       <c r="B221" s="2" t="n">
         <v>4</v>
@@ -6431,18 +6431,18 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_6</t>
+          <t>Eye/Eye_4</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>眼睛-6</t>
+          <t>眼睛-4</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>4050007</v>
+        <v>4050005</v>
       </c>
       <c r="B222" s="2" t="n">
         <v>4</v>
@@ -6455,18 +6455,18 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_7</t>
+          <t>Eye/Eye_5</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>眼睛-7</t>
+          <t>眼睛-5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>4050008</v>
+        <v>4050006</v>
       </c>
       <c r="B223" s="2" t="n">
         <v>4</v>
@@ -6479,18 +6479,18 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_8</t>
+          <t>Eye/Eye_6</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>眼睛-8</t>
+          <t>眼睛-6</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>4050009</v>
+        <v>4050007</v>
       </c>
       <c r="B224" s="2" t="n">
         <v>4</v>
@@ -6503,18 +6503,18 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_9</t>
+          <t>Eye/Eye_7</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>眼睛-9</t>
+          <t>眼睛-7</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>4050010</v>
+        <v>4050008</v>
       </c>
       <c r="B225" s="2" t="n">
         <v>4</v>
@@ -6527,18 +6527,18 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_10</t>
+          <t>Eye/Eye_8</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>眼睛-10</t>
+          <t>眼睛-8</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>4060001</v>
+        <v>4050009</v>
       </c>
       <c r="B226" s="2" t="n">
         <v>4</v>
@@ -6547,22 +6547,22 @@
         <v>0</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_1</t>
+          <t>Eye/Eye_9</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-1</t>
+          <t>眼睛-9</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>4060002</v>
+        <v>4050010</v>
       </c>
       <c r="B227" s="2" t="n">
         <v>4</v>
@@ -6571,22 +6571,22 @@
         <v>0</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_2</t>
+          <t>Eye/Eye_10</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-2</t>
+          <t>眼睛-10</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>4060003</v>
+        <v>4060001</v>
       </c>
       <c r="B228" s="2" t="n">
         <v>4</v>
@@ -6599,18 +6599,18 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_3</t>
+          <t>Mouth/Mouth_1</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-3</t>
+          <t>嘴巴-1</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>4060004</v>
+        <v>4060002</v>
       </c>
       <c r="B229" s="2" t="n">
         <v>4</v>
@@ -6623,18 +6623,18 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_4</t>
+          <t>Mouth/Mouth_2</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-4</t>
+          <t>嘴巴-2</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>4060005</v>
+        <v>4060003</v>
       </c>
       <c r="B230" s="2" t="n">
         <v>4</v>
@@ -6647,18 +6647,18 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_5</t>
+          <t>Mouth/Mouth_3</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-5</t>
+          <t>嘴巴-3</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>4060006</v>
+        <v>4060004</v>
       </c>
       <c r="B231" s="2" t="n">
         <v>4</v>
@@ -6671,18 +6671,18 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_6</t>
+          <t>Mouth/Mouth_4</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-6</t>
+          <t>嘴巴-4</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>4060007</v>
+        <v>4060005</v>
       </c>
       <c r="B232" s="2" t="n">
         <v>4</v>
@@ -6695,18 +6695,18 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_7</t>
+          <t>Mouth/Mouth_5</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-7</t>
+          <t>嘴巴-5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>4060008</v>
+        <v>4060006</v>
       </c>
       <c r="B233" s="2" t="n">
         <v>4</v>
@@ -6719,18 +6719,18 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_8</t>
+          <t>Mouth/Mouth_6</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-8</t>
+          <t>嘴巴-6</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>4060009</v>
+        <v>4060007</v>
       </c>
       <c r="B234" s="2" t="n">
         <v>4</v>
@@ -6743,18 +6743,18 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_9</t>
+          <t>Mouth/Mouth_7</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-9</t>
+          <t>嘴巴-7</t>
         </is>
       </c>
     </row>
     <row r="235" s="3">
       <c r="A235" s="2" t="n">
-        <v>4060010</v>
+        <v>4060008</v>
       </c>
       <c r="B235" s="2" t="n">
         <v>4</v>
@@ -6767,18 +6767,18 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_10</t>
+          <t>Mouth/Mouth_8</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-10</t>
+          <t>嘴巴-8</t>
         </is>
       </c>
     </row>
     <row r="236" s="3">
       <c r="A236" s="2" t="n">
-        <v>4070001</v>
+        <v>4060009</v>
       </c>
       <c r="B236" s="2" t="n">
         <v>4</v>
@@ -6787,22 +6787,22 @@
         <v>0</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_1</t>
+          <t>Mouth/Mouth_9</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>角-1</t>
+          <t>嘴巴-9</t>
         </is>
       </c>
     </row>
     <row r="237" s="3">
       <c r="A237" s="2" t="n">
-        <v>4070002</v>
+        <v>4060010</v>
       </c>
       <c r="B237" s="2" t="n">
         <v>4</v>
@@ -6811,22 +6811,22 @@
         <v>0</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_2</t>
+          <t>Mouth/Mouth_10</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>角-2</t>
+          <t>嘴巴-10</t>
         </is>
       </c>
     </row>
     <row r="238" s="3">
       <c r="A238" s="2" t="n">
-        <v>4070003</v>
+        <v>4070001</v>
       </c>
       <c r="B238" s="2" t="n">
         <v>4</v>
@@ -6839,18 +6839,18 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_3</t>
+          <t>Horn/Horn_1</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>角-3</t>
+          <t>角-1</t>
         </is>
       </c>
     </row>
     <row r="239" s="3">
       <c r="A239" s="2" t="n">
-        <v>4070004</v>
+        <v>4070002</v>
       </c>
       <c r="B239" s="2" t="n">
         <v>4</v>
@@ -6863,18 +6863,18 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_4</t>
+          <t>Horn/Horn_2</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>角-4</t>
+          <t>角-2</t>
         </is>
       </c>
     </row>
     <row r="240" s="3">
       <c r="A240" s="2" t="n">
-        <v>4070005</v>
+        <v>4070003</v>
       </c>
       <c r="B240" s="2" t="n">
         <v>4</v>
@@ -6887,18 +6887,18 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_5</t>
+          <t>Horn/Horn_3</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>角-5</t>
+          <t>角-3</t>
         </is>
       </c>
     </row>
     <row r="241" s="3">
       <c r="A241" s="2" t="n">
-        <v>4070006</v>
+        <v>4070004</v>
       </c>
       <c r="B241" s="2" t="n">
         <v>4</v>
@@ -6911,18 +6911,18 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_6</t>
+          <t>Horn/Horn_4</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>角-6</t>
+          <t>角-4</t>
         </is>
       </c>
     </row>
     <row r="242" s="3">
       <c r="A242" s="2" t="n">
-        <v>4070007</v>
+        <v>4070005</v>
       </c>
       <c r="B242" s="2" t="n">
         <v>4</v>
@@ -6935,18 +6935,18 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_7</t>
+          <t>Horn/Horn_5</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>角-7</t>
+          <t>角-5</t>
         </is>
       </c>
     </row>
     <row r="243" s="3">
       <c r="A243" s="2" t="n">
-        <v>4070008</v>
+        <v>4070006</v>
       </c>
       <c r="B243" s="2" t="n">
         <v>4</v>
@@ -6959,18 +6959,18 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_8</t>
+          <t>Horn/Horn_6</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>角-8</t>
+          <t>角-6</t>
         </is>
       </c>
     </row>
     <row r="244" s="3">
       <c r="A244" s="2" t="n">
-        <v>4070009</v>
+        <v>4070007</v>
       </c>
       <c r="B244" s="2" t="n">
         <v>4</v>
@@ -6983,18 +6983,18 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_9</t>
+          <t>Horn/Horn_7</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>角-9</t>
+          <t>角-7</t>
         </is>
       </c>
     </row>
     <row r="245" s="3">
       <c r="A245" s="2" t="n">
-        <v>4070010</v>
+        <v>4070008</v>
       </c>
       <c r="B245" s="2" t="n">
         <v>4</v>
@@ -7007,18 +7007,18 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_10</t>
+          <t>Horn/Horn_8</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>角-10</t>
+          <t>角-8</t>
         </is>
       </c>
     </row>
     <row r="246" s="3">
       <c r="A246" s="2" t="n">
-        <v>4080001</v>
+        <v>4070009</v>
       </c>
       <c r="B246" s="2" t="n">
         <v>4</v>
@@ -7027,22 +7027,22 @@
         <v>0</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>Wing/Wing_1</t>
+          <t>Horn/Horn_9</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>翅膀-1</t>
+          <t>角-9</t>
         </is>
       </c>
     </row>
     <row r="247" s="3">
       <c r="A247" s="2" t="n">
-        <v>4080002</v>
+        <v>4070010</v>
       </c>
       <c r="B247" s="2" t="n">
         <v>4</v>
@@ -7051,22 +7051,22 @@
         <v>0</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>Wing/Wing_2</t>
+          <t>Horn/Horn_10</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>翅膀-2</t>
+          <t>角-10</t>
         </is>
       </c>
     </row>
     <row r="248" s="3">
       <c r="A248" s="2" t="n">
-        <v>4080003</v>
+        <v>4080001</v>
       </c>
       <c r="B248" s="2" t="n">
         <v>4</v>
@@ -7079,18 +7079,18 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>Wing/Wing_3</t>
+          <t>Wing/Wing_1</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>翅膀-3</t>
+          <t>翅膀-1</t>
         </is>
       </c>
     </row>
     <row r="249" s="3">
       <c r="A249" s="2" t="n">
-        <v>4080004</v>
+        <v>4080002</v>
       </c>
       <c r="B249" s="2" t="n">
         <v>4</v>
@@ -7103,18 +7103,18 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>Wing/Wing_4</t>
+          <t>Wing/Wing_2</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>翅膀-4</t>
+          <t>翅膀-2</t>
         </is>
       </c>
     </row>
     <row r="250" s="3">
       <c r="A250" s="2" t="n">
-        <v>4500003</v>
+        <v>4080003</v>
       </c>
       <c r="B250" s="2" t="n">
         <v>4</v>
@@ -7123,22 +7123,22 @@
         <v>0</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_3</t>
+          <t>Wing/Wing_3</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>帽子-3</t>
+          <t>翅膀-3</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>4510001</v>
+        <v>4080004</v>
       </c>
       <c r="B251" s="2" t="n">
         <v>4</v>
@@ -7147,22 +7147,22 @@
         <v>0</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_1</t>
+          <t>Wing/Wing_4</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>衣服-1</t>
+          <t>翅膀-4</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>4510002</v>
+        <v>4500003</v>
       </c>
       <c r="B252" s="2" t="n">
         <v>4</v>
@@ -7171,22 +7171,22 @@
         <v>0</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_2</t>
+          <t>Hat/Hat_3</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>衣服-2</t>
+          <t>帽子-3</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>4510003</v>
+        <v>4510001</v>
       </c>
       <c r="B253" s="2" t="n">
         <v>4</v>
@@ -7199,18 +7199,18 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_3</t>
+          <t>Clothes/Clothes_1</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>衣服-3</t>
+          <t>衣服-1</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>4510004</v>
+        <v>4510002</v>
       </c>
       <c r="B254" s="2" t="n">
         <v>4</v>
@@ -7223,18 +7223,18 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_4</t>
+          <t>Clothes/Clothes_2</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>衣服-4</t>
+          <t>衣服-2</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>4510005</v>
+        <v>4510003</v>
       </c>
       <c r="B255" s="2" t="n">
         <v>4</v>
@@ -7247,18 +7247,18 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_5</t>
+          <t>Clothes/Clothes_3</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>衣服-5</t>
+          <t>衣服-3</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>4510006</v>
+        <v>4510004</v>
       </c>
       <c r="B256" s="2" t="n">
         <v>4</v>
@@ -7271,18 +7271,18 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_6</t>
+          <t>Clothes/Clothes_4</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>衣服-6</t>
+          <t>衣服-4</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>4520001</v>
+        <v>4510005</v>
       </c>
       <c r="B257" s="2" t="n">
         <v>4</v>
@@ -7291,22 +7291,22 @@
         <v>0</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_1</t>
+          <t>Clothes/Clothes_5</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>裤子1</t>
+          <t>衣服-5</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>4520002</v>
+        <v>4510006</v>
       </c>
       <c r="B258" s="2" t="n">
         <v>4</v>
@@ -7315,22 +7315,22 @@
         <v>0</v>
       </c>
       <c r="D258" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_2</t>
+          <t>Clothes/Clothes_6</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>裤子2</t>
+          <t>衣服-6</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>4520003</v>
+        <v>4520001</v>
       </c>
       <c r="B259" s="2" t="n">
         <v>4</v>
@@ -7343,18 +7343,18 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_3</t>
+          <t>Pants/Pants_1</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>裤子3</t>
+          <t>裤子1</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>4520004</v>
+        <v>4520002</v>
       </c>
       <c r="B260" s="2" t="n">
         <v>4</v>
@@ -7367,18 +7367,18 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_4</t>
+          <t>Pants/Pants_2</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>裤子4</t>
+          <t>裤子2</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>4900001</v>
+        <v>4520003</v>
       </c>
       <c r="B261" s="2" t="n">
         <v>4</v>
@@ -7387,22 +7387,22 @@
         <v>0</v>
       </c>
       <c r="D261" s="2" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_1</t>
+          <t>Pants/Pants_3</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>武器-左-1</t>
+          <t>裤子3</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>4900002</v>
+        <v>4520004</v>
       </c>
       <c r="B262" s="2" t="n">
         <v>4</v>
@@ -7411,22 +7411,22 @@
         <v>0</v>
       </c>
       <c r="D262" s="2" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_2</t>
+          <t>Pants/Pants_4</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>武器-左-2</t>
+          <t>裤子4</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>4900003</v>
+        <v>4900001</v>
       </c>
       <c r="B263" s="2" t="n">
         <v>4</v>
@@ -7439,18 +7439,18 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_3</t>
+          <t>Weapon/Weapon_L_1</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>武器-左-3</t>
+          <t>武器-左-1</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>4900004</v>
+        <v>4900002</v>
       </c>
       <c r="B264" s="2" t="n">
         <v>4</v>
@@ -7463,18 +7463,18 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_4</t>
+          <t>Weapon/Weapon_L_2</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>武器-左-4</t>
+          <t>武器-左-2</t>
         </is>
       </c>
     </row>
     <row r="265" s="3">
       <c r="A265" s="2" t="n">
-        <v>4900005</v>
+        <v>4900003</v>
       </c>
       <c r="B265" s="2" t="n">
         <v>4</v>
@@ -7487,66 +7487,66 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_5</t>
+          <t>Weapon/Weapon_L_3</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>武器-左-5</t>
+          <t>武器-左-3</t>
         </is>
       </c>
     </row>
     <row r="266" s="3">
       <c r="A266" s="2" t="n">
-        <v>5000001</v>
+        <v>4900004</v>
       </c>
       <c r="B266" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C266" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>Base/Base_1</t>
+          <t>Weapon/Weapon_L_4</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>牛头人-基础</t>
+          <t>武器-左-4</t>
         </is>
       </c>
     </row>
     <row r="267" s="3">
       <c r="A267" s="2" t="n">
-        <v>5050001</v>
+        <v>4900005</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C267" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_1</t>
+          <t>Weapon/Weapon_L_5</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-1</t>
+          <t>武器-左-5</t>
         </is>
       </c>
     </row>
     <row r="268" s="3">
       <c r="A268" s="2" t="n">
-        <v>5050002</v>
+        <v>5000001</v>
       </c>
       <c r="B268" s="2" t="n">
         <v>5</v>
@@ -7555,22 +7555,22 @@
         <v>0</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_2</t>
+          <t>Base/Base_1</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-2</t>
+          <t>牛头人-基础</t>
         </is>
       </c>
     </row>
     <row r="269" s="3">
       <c r="A269" s="2" t="n">
-        <v>5050003</v>
+        <v>5050001</v>
       </c>
       <c r="B269" s="2" t="n">
         <v>5</v>
@@ -7583,18 +7583,18 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_3</t>
+          <t>Eye/Eye_1</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-3</t>
+          <t>牛头人-眼睛-1</t>
         </is>
       </c>
     </row>
     <row r="270" s="3">
       <c r="A270" s="2" t="n">
-        <v>5050004</v>
+        <v>5050002</v>
       </c>
       <c r="B270" s="2" t="n">
         <v>5</v>
@@ -7607,18 +7607,18 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_4</t>
+          <t>Eye/Eye_2</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-4</t>
+          <t>牛头人-眼睛-2</t>
         </is>
       </c>
     </row>
     <row r="271" s="3">
       <c r="A271" s="2" t="n">
-        <v>5050005</v>
+        <v>5050003</v>
       </c>
       <c r="B271" s="2" t="n">
         <v>5</v>
@@ -7631,18 +7631,18 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_5</t>
+          <t>Eye/Eye_3</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-5</t>
+          <t>牛头人-眼睛-3</t>
         </is>
       </c>
     </row>
     <row r="272" s="3">
       <c r="A272" s="2" t="n">
-        <v>5050006</v>
+        <v>5050004</v>
       </c>
       <c r="B272" s="2" t="n">
         <v>5</v>
@@ -7655,18 +7655,18 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_6</t>
+          <t>Eye/Eye_4</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-6</t>
+          <t>牛头人-眼睛-4</t>
         </is>
       </c>
     </row>
     <row r="273" s="3">
       <c r="A273" s="2" t="n">
-        <v>5050007</v>
+        <v>5050005</v>
       </c>
       <c r="B273" s="2" t="n">
         <v>5</v>
@@ -7679,18 +7679,18 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_7</t>
+          <t>Eye/Eye_5</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-7</t>
+          <t>牛头人-眼睛-5</t>
         </is>
       </c>
     </row>
     <row r="274" s="3">
       <c r="A274" s="2" t="n">
-        <v>5050008</v>
+        <v>5050006</v>
       </c>
       <c r="B274" s="2" t="n">
         <v>5</v>
@@ -7703,18 +7703,18 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_8</t>
+          <t>Eye/Eye_6</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-8</t>
+          <t>牛头人-眼睛-6</t>
         </is>
       </c>
     </row>
     <row r="275" s="3">
       <c r="A275" s="2" t="n">
-        <v>5050009</v>
+        <v>5050007</v>
       </c>
       <c r="B275" s="2" t="n">
         <v>5</v>
@@ -7727,18 +7727,18 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_9</t>
+          <t>Eye/Eye_7</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-9</t>
+          <t>牛头人-眼睛-7</t>
         </is>
       </c>
     </row>
     <row r="276" s="3">
       <c r="A276" s="2" t="n">
-        <v>5050010</v>
+        <v>5050008</v>
       </c>
       <c r="B276" s="2" t="n">
         <v>5</v>
@@ -7751,18 +7751,18 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_10</t>
+          <t>Eye/Eye_8</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-10</t>
+          <t>牛头人-眼睛-8</t>
         </is>
       </c>
     </row>
     <row r="277" s="3">
       <c r="A277" s="2" t="n">
-        <v>5050011</v>
+        <v>5050009</v>
       </c>
       <c r="B277" s="2" t="n">
         <v>5</v>
@@ -7775,18 +7775,18 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_11</t>
+          <t>Eye/Eye_9</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>牛头人-眼睛-11</t>
+          <t>牛头人-眼睛-9</t>
         </is>
       </c>
     </row>
     <row r="278" s="3">
       <c r="A278" s="2" t="n">
-        <v>5070001</v>
+        <v>5050010</v>
       </c>
       <c r="B278" s="2" t="n">
         <v>5</v>
@@ -7795,22 +7795,22 @@
         <v>0</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_1</t>
+          <t>Eye/Eye_10</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>角-1</t>
+          <t>牛头人-眼睛-10</t>
         </is>
       </c>
     </row>
     <row r="279" s="3">
       <c r="A279" s="2" t="n">
-        <v>5070002</v>
+        <v>5050011</v>
       </c>
       <c r="B279" s="2" t="n">
         <v>5</v>
@@ -7819,22 +7819,22 @@
         <v>0</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_2</t>
+          <t>Eye/Eye_11</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>角-2</t>
+          <t>牛头人-眼睛-11</t>
         </is>
       </c>
     </row>
     <row r="280" s="3">
       <c r="A280" s="2" t="n">
-        <v>5070003</v>
+        <v>5070001</v>
       </c>
       <c r="B280" s="2" t="n">
         <v>5</v>
@@ -7847,18 +7847,18 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_3</t>
+          <t>Horn/Horn_1</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>角-3</t>
+          <t>角-1</t>
         </is>
       </c>
     </row>
     <row r="281" s="3">
       <c r="A281" s="2" t="n">
-        <v>5070004</v>
+        <v>5070002</v>
       </c>
       <c r="B281" s="2" t="n">
         <v>5</v>
@@ -7871,18 +7871,18 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_4</t>
+          <t>Horn/Horn_2</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>角-4</t>
+          <t>角-2</t>
         </is>
       </c>
     </row>
     <row r="282" s="3">
       <c r="A282" s="2" t="n">
-        <v>5070005</v>
+        <v>5070003</v>
       </c>
       <c r="B282" s="2" t="n">
         <v>5</v>
@@ -7895,18 +7895,18 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>Horn/Horn_5</t>
+          <t>Horn/Horn_3</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>角-5</t>
+          <t>角-3</t>
         </is>
       </c>
     </row>
     <row r="283" s="3">
       <c r="A283" s="2" t="n">
-        <v>5090001</v>
+        <v>5070004</v>
       </c>
       <c r="B283" s="2" t="n">
         <v>5</v>
@@ -7915,22 +7915,22 @@
         <v>0</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>NoseRing/NoseRing_1</t>
+          <t>Horn/Horn_4</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>鼻环-1</t>
+          <t>角-4</t>
         </is>
       </c>
     </row>
     <row r="284" s="3">
       <c r="A284" s="2" t="n">
-        <v>5090002</v>
+        <v>5070005</v>
       </c>
       <c r="B284" s="2" t="n">
         <v>5</v>
@@ -7939,22 +7939,22 @@
         <v>0</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>NoseRing/NoseRing_2</t>
+          <t>Horn/Horn_5</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>鼻环-2</t>
+          <t>角-5</t>
         </is>
       </c>
     </row>
     <row r="285" s="3">
       <c r="A285" s="2" t="n">
-        <v>5090003</v>
+        <v>5090001</v>
       </c>
       <c r="B285" s="2" t="n">
         <v>5</v>
@@ -7967,18 +7967,18 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>NoseRing/NoseRing_3</t>
+          <t>NoseRing/NoseRing_1</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>鼻环-3</t>
+          <t>鼻环-1</t>
         </is>
       </c>
     </row>
     <row r="286" s="3">
       <c r="A286" s="2" t="n">
-        <v>5090004</v>
+        <v>5090002</v>
       </c>
       <c r="B286" s="2" t="n">
         <v>5</v>
@@ -7991,18 +7991,18 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>NoseRing/NoseRing_4</t>
+          <t>NoseRing/NoseRing_2</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>鼻环-4</t>
+          <t>鼻环-2</t>
         </is>
       </c>
     </row>
     <row r="287" s="3">
       <c r="A287" s="2" t="n">
-        <v>5090005</v>
+        <v>5090003</v>
       </c>
       <c r="B287" s="2" t="n">
         <v>5</v>
@@ -8015,18 +8015,18 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>NoseRing/NoseRing_5</t>
+          <t>NoseRing/NoseRing_3</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>鼻环-5</t>
+          <t>鼻环-3</t>
         </is>
       </c>
     </row>
     <row r="288" s="3">
       <c r="A288" s="2" t="n">
-        <v>5500001</v>
+        <v>5090004</v>
       </c>
       <c r="B288" s="2" t="n">
         <v>5</v>
@@ -8035,22 +8035,22 @@
         <v>0</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_1</t>
+          <t>NoseRing/NoseRing_4</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>牛头人帽子-1</t>
+          <t>鼻环-4</t>
         </is>
       </c>
     </row>
     <row r="289" s="3">
       <c r="A289" s="2" t="n">
-        <v>5500002</v>
+        <v>5090005</v>
       </c>
       <c r="B289" s="2" t="n">
         <v>5</v>
@@ -8059,22 +8059,22 @@
         <v>0</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_2</t>
+          <t>NoseRing/NoseRing_5</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>牛头人帽子-2</t>
+          <t>鼻环-5</t>
         </is>
       </c>
     </row>
     <row r="290" s="3">
       <c r="A290" s="2" t="n">
-        <v>5500003</v>
+        <v>5500001</v>
       </c>
       <c r="B290" s="2" t="n">
         <v>5</v>
@@ -8087,18 +8087,18 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_3</t>
+          <t>Hat/Hat_1</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>牛头人帽子-3</t>
+          <t>牛头人帽子-1</t>
         </is>
       </c>
     </row>
     <row r="291" s="3">
       <c r="A291" s="2" t="n">
-        <v>5510001</v>
+        <v>5500002</v>
       </c>
       <c r="B291" s="2" t="n">
         <v>5</v>
@@ -8107,22 +8107,22 @@
         <v>0</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_1</t>
+          <t>Hat/Hat_2</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>牛头人-衣服-银制盔甲</t>
+          <t>牛头人帽子-2</t>
         </is>
       </c>
     </row>
     <row r="292" s="3">
       <c r="A292" s="2" t="n">
-        <v>5510002</v>
+        <v>5500003</v>
       </c>
       <c r="B292" s="2" t="n">
         <v>5</v>
@@ -8131,22 +8131,22 @@
         <v>0</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_2</t>
+          <t>Hat/Hat_3</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>牛头人-衣服-皮甲</t>
+          <t>牛头人帽子-3</t>
         </is>
       </c>
     </row>
     <row r="293" s="3">
       <c r="A293" s="2" t="n">
-        <v>5510003</v>
+        <v>5510001</v>
       </c>
       <c r="B293" s="2" t="n">
         <v>5</v>
@@ -8159,18 +8159,18 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_3</t>
+          <t>Clothes/Clothes_1</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>牛头人-衣服-皮带胸甲</t>
+          <t>牛头人-衣服-银制盔甲</t>
         </is>
       </c>
     </row>
     <row r="294" s="3">
       <c r="A294" s="2" t="n">
-        <v>5520001</v>
+        <v>5510002</v>
       </c>
       <c r="B294" s="2" t="n">
         <v>5</v>
@@ -8179,22 +8179,22 @@
         <v>0</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_1</t>
+          <t>Clothes/Clothes_2</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>裤子1</t>
+          <t>牛头人-衣服-皮甲</t>
         </is>
       </c>
     </row>
     <row r="295" s="3">
       <c r="A295" s="2" t="n">
-        <v>5520002</v>
+        <v>5510003</v>
       </c>
       <c r="B295" s="2" t="n">
         <v>5</v>
@@ -8203,22 +8203,22 @@
         <v>0</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_2</t>
+          <t>Clothes/Clothes_3</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>裤子2</t>
+          <t>牛头人-衣服-皮带胸甲</t>
         </is>
       </c>
     </row>
     <row r="296" s="3">
       <c r="A296" s="2" t="n">
-        <v>5910001</v>
+        <v>5520001</v>
       </c>
       <c r="B296" s="2" t="n">
         <v>5</v>
@@ -8227,22 +8227,22 @@
         <v>0</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_1</t>
+          <t>Pants/Pants_1</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>石头</t>
+          <t>裤子1</t>
         </is>
       </c>
     </row>
     <row r="297" s="3">
       <c r="A297" s="2" t="n">
-        <v>5910002</v>
+        <v>5520002</v>
       </c>
       <c r="B297" s="2" t="n">
         <v>5</v>
@@ -8251,22 +8251,22 @@
         <v>0</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_2</t>
+          <t>Pants/Pants_2</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>裤子2</t>
         </is>
       </c>
     </row>
     <row r="298" s="3">
       <c r="A298" s="2" t="n">
-        <v>5910003</v>
+        <v>5910001</v>
       </c>
       <c r="B298" s="2" t="n">
         <v>5</v>
@@ -8279,66 +8279,66 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_3</t>
+          <t>Weapon/Weapon_R_1</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>宝箱</t>
+          <t>石头</t>
         </is>
       </c>
     </row>
     <row r="299" s="3">
       <c r="A299" s="2" t="n">
-        <v>6000001</v>
+        <v>5910002</v>
       </c>
       <c r="B299" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C299" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Base/Base_1</t>
+          <t>Weapon/Weapon_R_2</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>哥布林-基础</t>
+          <t>魔晶</t>
         </is>
       </c>
     </row>
     <row r="300" s="3">
       <c r="A300" s="2" t="n">
-        <v>6050001</v>
+        <v>5910003</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C300" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_1</t>
+          <t>Weapon/Weapon_R_3</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>哥布林-眼睛-1</t>
+          <t>宝箱</t>
         </is>
       </c>
     </row>
     <row r="301" s="3">
       <c r="A301" s="2" t="n">
-        <v>6050002</v>
+        <v>6000001</v>
       </c>
       <c r="B301" s="2" t="n">
         <v>6</v>
@@ -8347,22 +8347,22 @@
         <v>0</v>
       </c>
       <c r="D301" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_2</t>
+          <t>Base/Base_1</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>哥布林-眼睛-2</t>
+          <t>哥布林-基础</t>
         </is>
       </c>
     </row>
     <row r="302" s="3">
       <c r="A302" s="2" t="n">
-        <v>6050003</v>
+        <v>6050001</v>
       </c>
       <c r="B302" s="2" t="n">
         <v>6</v>
@@ -8375,18 +8375,18 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_3</t>
+          <t>Eye/Eye_1</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>哥布林-眼睛-3</t>
+          <t>哥布林-眼睛-1</t>
         </is>
       </c>
     </row>
     <row r="303" s="3">
       <c r="A303" s="2" t="n">
-        <v>6050004</v>
+        <v>6050002</v>
       </c>
       <c r="B303" s="2" t="n">
         <v>6</v>
@@ -8399,18 +8399,18 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_4</t>
+          <t>Eye/Eye_2</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>哥布林-眼睛-4</t>
+          <t>哥布林-眼睛-2</t>
         </is>
       </c>
     </row>
     <row r="304" s="3">
       <c r="A304" s="2" t="n">
-        <v>6050005</v>
+        <v>6050003</v>
       </c>
       <c r="B304" s="2" t="n">
         <v>6</v>
@@ -8423,18 +8423,18 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_5</t>
+          <t>Eye/Eye_3</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>哥布林-眼睛-5</t>
+          <t>哥布林-眼睛-3</t>
         </is>
       </c>
     </row>
     <row r="305" s="3">
       <c r="A305" s="2" t="n">
-        <v>6050006</v>
+        <v>6050004</v>
       </c>
       <c r="B305" s="2" t="n">
         <v>6</v>
@@ -8447,18 +8447,18 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_6</t>
+          <t>Eye/Eye_4</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>哥布林-眼睛-6</t>
+          <t>哥布林-眼睛-4</t>
         </is>
       </c>
     </row>
     <row r="306" s="3">
       <c r="A306" s="2" t="n">
-        <v>6050007</v>
+        <v>6050005</v>
       </c>
       <c r="B306" s="2" t="n">
         <v>6</v>
@@ -8471,18 +8471,18 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_7</t>
+          <t>Eye/Eye_5</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>哥布林-眼睛-7</t>
+          <t>哥布林-眼睛-5</t>
         </is>
       </c>
     </row>
     <row r="307" s="3">
       <c r="A307" s="2" t="n">
-        <v>6050008</v>
+        <v>6050006</v>
       </c>
       <c r="B307" s="2" t="n">
         <v>6</v>
@@ -8495,18 +8495,18 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_8</t>
+          <t>Eye/Eye_6</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>哥布林-眼睛-8</t>
+          <t>哥布林-眼睛-6</t>
         </is>
       </c>
     </row>
     <row r="308" s="3">
       <c r="A308" s="2" t="n">
-        <v>6050009</v>
+        <v>6050007</v>
       </c>
       <c r="B308" s="2" t="n">
         <v>6</v>
@@ -8519,18 +8519,18 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_9</t>
+          <t>Eye/Eye_7</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>哥布林-眼睛-9</t>
+          <t>哥布林-眼睛-7</t>
         </is>
       </c>
     </row>
     <row r="309" s="3">
       <c r="A309" s="2" t="n">
-        <v>6050010</v>
+        <v>6050008</v>
       </c>
       <c r="B309" s="2" t="n">
         <v>6</v>
@@ -8543,18 +8543,18 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_10</t>
+          <t>Eye/Eye_8</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>哥布林-眼睛-10</t>
+          <t>哥布林-眼睛-8</t>
         </is>
       </c>
     </row>
     <row r="310" s="3">
       <c r="A310" s="2" t="n">
-        <v>6060001</v>
+        <v>6050009</v>
       </c>
       <c r="B310" s="2" t="n">
         <v>6</v>
@@ -8563,22 +8563,22 @@
         <v>0</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_1</t>
+          <t>Eye/Eye_9</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-1</t>
+          <t>哥布林-眼睛-9</t>
         </is>
       </c>
     </row>
     <row r="311" s="3">
       <c r="A311" s="2" t="n">
-        <v>6060002</v>
+        <v>6050010</v>
       </c>
       <c r="B311" s="2" t="n">
         <v>6</v>
@@ -8587,22 +8587,22 @@
         <v>0</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_2</t>
+          <t>Eye/Eye_10</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-2</t>
+          <t>哥布林-眼睛-10</t>
         </is>
       </c>
     </row>
     <row r="312" s="3">
       <c r="A312" s="2" t="n">
-        <v>6060003</v>
+        <v>6060001</v>
       </c>
       <c r="B312" s="2" t="n">
         <v>6</v>
@@ -8615,18 +8615,18 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_3</t>
+          <t>Mouth/Mouth_1</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-3</t>
+          <t>嘴巴-1</t>
         </is>
       </c>
     </row>
     <row r="313" s="3">
       <c r="A313" s="2" t="n">
-        <v>6060004</v>
+        <v>6060002</v>
       </c>
       <c r="B313" s="2" t="n">
         <v>6</v>
@@ -8639,18 +8639,18 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_4</t>
+          <t>Mouth/Mouth_2</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-4</t>
+          <t>嘴巴-2</t>
         </is>
       </c>
     </row>
     <row r="314" s="3">
       <c r="A314" s="2" t="n">
-        <v>6060005</v>
+        <v>6060003</v>
       </c>
       <c r="B314" s="2" t="n">
         <v>6</v>
@@ -8663,18 +8663,18 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_5</t>
+          <t>Mouth/Mouth_3</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-5</t>
+          <t>嘴巴-3</t>
         </is>
       </c>
     </row>
     <row r="315" s="3">
       <c r="A315" s="2" t="n">
-        <v>6060006</v>
+        <v>6060004</v>
       </c>
       <c r="B315" s="2" t="n">
         <v>6</v>
@@ -8687,18 +8687,18 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_6</t>
+          <t>Mouth/Mouth_4</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-6</t>
+          <t>嘴巴-4</t>
         </is>
       </c>
     </row>
     <row r="316" s="3">
       <c r="A316" s="2" t="n">
-        <v>6060007</v>
+        <v>6060005</v>
       </c>
       <c r="B316" s="2" t="n">
         <v>6</v>
@@ -8711,18 +8711,18 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_7</t>
+          <t>Mouth/Mouth_5</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-7</t>
+          <t>嘴巴-5</t>
         </is>
       </c>
     </row>
     <row r="317" s="3">
       <c r="A317" s="2" t="n">
-        <v>6060008</v>
+        <v>6060006</v>
       </c>
       <c r="B317" s="2" t="n">
         <v>6</v>
@@ -8735,18 +8735,18 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_8</t>
+          <t>Mouth/Mouth_6</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-8</t>
+          <t>嘴巴-6</t>
         </is>
       </c>
     </row>
     <row r="318" s="3">
       <c r="A318" s="2" t="n">
-        <v>6060009</v>
+        <v>6060007</v>
       </c>
       <c r="B318" s="2" t="n">
         <v>6</v>
@@ -8759,18 +8759,18 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_9</t>
+          <t>Mouth/Mouth_7</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-9</t>
+          <t>嘴巴-7</t>
         </is>
       </c>
     </row>
     <row r="319" s="3">
       <c r="A319" s="2" t="n">
-        <v>6060010</v>
+        <v>6060008</v>
       </c>
       <c r="B319" s="2" t="n">
         <v>6</v>
@@ -8783,18 +8783,18 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_10</t>
+          <t>Mouth/Mouth_8</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-10</t>
+          <t>嘴巴-8</t>
         </is>
       </c>
     </row>
     <row r="320" s="3">
       <c r="A320" s="2" t="n">
-        <v>6500001</v>
+        <v>6060009</v>
       </c>
       <c r="B320" s="2" t="n">
         <v>6</v>
@@ -8803,22 +8803,22 @@
         <v>0</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_1</t>
+          <t>Mouth/Mouth_9</t>
         </is>
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>哥布林帽子-1</t>
+          <t>嘴巴-9</t>
         </is>
       </c>
     </row>
     <row r="321" s="3">
       <c r="A321" s="2" t="n">
-        <v>6500002</v>
+        <v>6060010</v>
       </c>
       <c r="B321" s="2" t="n">
         <v>6</v>
@@ -8827,22 +8827,22 @@
         <v>0</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_2</t>
+          <t>Mouth/Mouth_10</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>哥布林帽子-2</t>
+          <t>嘴巴-10</t>
         </is>
       </c>
     </row>
     <row r="322" s="3">
       <c r="A322" s="2" t="n">
-        <v>6500003</v>
+        <v>6500001</v>
       </c>
       <c r="B322" s="2" t="n">
         <v>6</v>
@@ -8855,18 +8855,18 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_3</t>
+          <t>Hat/Hat_1</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>哥布林帽子-3</t>
+          <t>哥布林帽子-1</t>
         </is>
       </c>
     </row>
     <row r="323" s="3">
       <c r="A323" s="2" t="n">
-        <v>6500004</v>
+        <v>6500002</v>
       </c>
       <c r="B323" s="2" t="n">
         <v>6</v>
@@ -8879,18 +8879,18 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_4</t>
+          <t>Hat/Hat_2</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>哥布林帽子-4</t>
+          <t>哥布林帽子-2</t>
         </is>
       </c>
     </row>
     <row r="324" s="3">
       <c r="A324" s="2" t="n">
-        <v>6500005</v>
+        <v>6500003</v>
       </c>
       <c r="B324" s="2" t="n">
         <v>6</v>
@@ -8903,18 +8903,18 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_5</t>
+          <t>Hat/Hat_3</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>哥布林帽子-5</t>
+          <t>哥布林帽子-3</t>
         </is>
       </c>
     </row>
     <row r="325" s="3">
       <c r="A325" s="2" t="n">
-        <v>6500006</v>
+        <v>6500004</v>
       </c>
       <c r="B325" s="2" t="n">
         <v>6</v>
@@ -8927,18 +8927,18 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_6</t>
+          <t>Hat/Hat_4</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>哥布林帽子-6</t>
+          <t>哥布林帽子-4</t>
         </is>
       </c>
     </row>
     <row r="326" s="3">
       <c r="A326" s="2" t="n">
-        <v>6500007</v>
+        <v>6500005</v>
       </c>
       <c r="B326" s="2" t="n">
         <v>6</v>
@@ -8951,18 +8951,18 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_7</t>
+          <t>Hat/Hat_5</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>哥布林帽子-7</t>
+          <t>哥布林帽子-5</t>
         </is>
       </c>
     </row>
     <row r="327" s="3">
       <c r="A327" s="2" t="n">
-        <v>6500008</v>
+        <v>6500006</v>
       </c>
       <c r="B327" s="2" t="n">
         <v>6</v>
@@ -8975,18 +8975,18 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_8</t>
+          <t>Hat/Hat_6</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>哥布林帽子-8</t>
+          <t>哥布林帽子-6</t>
         </is>
       </c>
     </row>
     <row r="328" s="3">
       <c r="A328" s="2" t="n">
-        <v>6500009</v>
+        <v>6500007</v>
       </c>
       <c r="B328" s="2" t="n">
         <v>6</v>
@@ -8999,18 +8999,18 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_9</t>
+          <t>Hat/Hat_7</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>哥布林帽子-9</t>
+          <t>哥布林帽子-7</t>
         </is>
       </c>
     </row>
     <row r="329" s="3">
       <c r="A329" s="2" t="n">
-        <v>6500010</v>
+        <v>6500008</v>
       </c>
       <c r="B329" s="2" t="n">
         <v>6</v>
@@ -9023,18 +9023,18 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_10</t>
+          <t>Hat/Hat_8</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>哥布林帽子-10</t>
+          <t>哥布林帽子-8</t>
         </is>
       </c>
     </row>
     <row r="330" s="3">
       <c r="A330" s="2" t="n">
-        <v>6510001</v>
+        <v>6500009</v>
       </c>
       <c r="B330" s="2" t="n">
         <v>6</v>
@@ -9043,22 +9043,22 @@
         <v>0</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_1</t>
+          <t>Hat/Hat_9</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>哥布林-衣服-布衣</t>
+          <t>哥布林帽子-9</t>
         </is>
       </c>
     </row>
     <row r="331" s="3">
       <c r="A331" s="2" t="n">
-        <v>6510002</v>
+        <v>6500010</v>
       </c>
       <c r="B331" s="2" t="n">
         <v>6</v>
@@ -9067,22 +9067,22 @@
         <v>0</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_2</t>
+          <t>Hat/Hat_10</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>哥布林-衣服-质朴蓝衣</t>
+          <t>哥布林帽子-10</t>
         </is>
       </c>
     </row>
     <row r="332" s="3">
       <c r="A332" s="2" t="n">
-        <v>6520001</v>
+        <v>6510001</v>
       </c>
       <c r="B332" s="2" t="n">
         <v>6</v>
@@ -9091,22 +9091,22 @@
         <v>0</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_1</t>
+          <t>Clothes/Clothes_1</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>裤子1</t>
+          <t>哥布林-衣服-布衣</t>
         </is>
       </c>
     </row>
     <row r="333" s="3">
       <c r="A333" s="2" t="n">
-        <v>6520002</v>
+        <v>6510002</v>
       </c>
       <c r="B333" s="2" t="n">
         <v>6</v>
@@ -9115,22 +9115,22 @@
         <v>0</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_2</t>
+          <t>Clothes/Clothes_2</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>裤子2</t>
+          <t>哥布林-衣服-质朴蓝衣</t>
         </is>
       </c>
     </row>
     <row r="334" s="3">
       <c r="A334" s="2" t="n">
-        <v>6520003</v>
+        <v>6520001</v>
       </c>
       <c r="B334" s="2" t="n">
         <v>6</v>
@@ -9143,18 +9143,18 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_3</t>
+          <t>Pants/Pants_1</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>裤子3</t>
+          <t>裤子1</t>
         </is>
       </c>
     </row>
     <row r="335" s="3">
       <c r="A335" s="2" t="n">
-        <v>6520004</v>
+        <v>6520002</v>
       </c>
       <c r="B335" s="2" t="n">
         <v>6</v>
@@ -9167,18 +9167,18 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_4</t>
+          <t>Pants/Pants_2</t>
         </is>
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>裤子4</t>
+          <t>裤子2</t>
         </is>
       </c>
     </row>
     <row r="336" s="3">
       <c r="A336" s="2" t="n">
-        <v>6520005</v>
+        <v>6520003</v>
       </c>
       <c r="B336" s="2" t="n">
         <v>6</v>
@@ -9191,18 +9191,18 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_5</t>
+          <t>Pants/Pants_3</t>
         </is>
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>裤子5</t>
+          <t>裤子3</t>
         </is>
       </c>
     </row>
     <row r="337" ht="12" customHeight="1" s="3">
       <c r="A337" s="2" t="n">
-        <v>6800001</v>
+        <v>6520004</v>
       </c>
       <c r="B337" s="2" t="n">
         <v>6</v>
@@ -9211,22 +9211,22 @@
         <v>0</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>Other/Line_1</t>
+          <t>Pants/Pants_4</t>
         </is>
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>弓箭线</t>
+          <t>裤子4</t>
         </is>
       </c>
     </row>
     <row r="338" s="3">
       <c r="A338" s="2" t="n">
-        <v>6910001</v>
+        <v>6520005</v>
       </c>
       <c r="B338" s="2" t="n">
         <v>6</v>
@@ -9235,22 +9235,22 @@
         <v>0</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_1</t>
+          <t>Pants/Pants_5</t>
         </is>
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-金刀</t>
+          <t>裤子5</t>
         </is>
       </c>
     </row>
     <row r="339" s="3">
       <c r="A339" s="2" t="n">
-        <v>6910002</v>
+        <v>6800001</v>
       </c>
       <c r="B339" s="2" t="n">
         <v>6</v>
@@ -9259,22 +9259,22 @@
         <v>0</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_2</t>
+          <t>Other/Line_1</t>
         </is>
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-木弓</t>
+          <t>弓箭线</t>
         </is>
       </c>
     </row>
     <row r="340" s="3">
       <c r="A340" s="2" t="n">
-        <v>6910003</v>
+        <v>6910001</v>
       </c>
       <c r="B340" s="2" t="n">
         <v>6</v>
@@ -9287,18 +9287,18 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_3</t>
+          <t>Weapon/Weapon_R_1</t>
         </is>
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-木法杖</t>
+          <t>哥布林-武器-金刀</t>
         </is>
       </c>
     </row>
     <row r="341" s="3">
       <c r="A341" s="2" t="n">
-        <v>6910004</v>
+        <v>6910002</v>
       </c>
       <c r="B341" s="2" t="n">
         <v>6</v>
@@ -9311,18 +9311,18 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_4</t>
+          <t>Weapon/Weapon_R_2</t>
         </is>
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-骷髅法杖</t>
+          <t>哥布林-武器-木弓</t>
         </is>
       </c>
     </row>
     <row r="342" s="3">
       <c r="A342" s="2" t="n">
-        <v>6910005</v>
+        <v>6910003</v>
       </c>
       <c r="B342" s="2" t="n">
         <v>6</v>
@@ -9335,18 +9335,18 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_5</t>
+          <t>Weapon/Weapon_R_3</t>
         </is>
       </c>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-十字法杖</t>
+          <t>哥布林-武器-木法杖</t>
         </is>
       </c>
     </row>
     <row r="343" s="3">
       <c r="A343" s="2" t="n">
-        <v>6910006</v>
+        <v>6910004</v>
       </c>
       <c r="B343" s="2" t="n">
         <v>6</v>
@@ -9359,18 +9359,18 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_6</t>
+          <t>Weapon/Weapon_R_4</t>
         </is>
       </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-蔚来法棍</t>
+          <t>哥布林-武器-骷髅法杖</t>
         </is>
       </c>
     </row>
     <row r="344" s="3">
       <c r="A344" s="2" t="n">
-        <v>6910007</v>
+        <v>6910005</v>
       </c>
       <c r="B344" s="2" t="n">
         <v>6</v>
@@ -9383,18 +9383,18 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_7</t>
+          <t>Weapon/Weapon_R_5</t>
         </is>
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-死亡之书</t>
+          <t>哥布林-武器-十字法杖</t>
         </is>
       </c>
     </row>
     <row r="345" s="3">
       <c r="A345" s="2" t="n">
-        <v>6910008</v>
+        <v>6910006</v>
       </c>
       <c r="B345" s="2" t="n">
         <v>6</v>
@@ -9407,18 +9407,18 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_8</t>
+          <t>Weapon/Weapon_R_6</t>
         </is>
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-猩红之酒</t>
+          <t>哥布林-武器-蔚来法棍</t>
         </is>
       </c>
     </row>
     <row r="346" s="3">
       <c r="A346" s="2" t="n">
-        <v>6910009</v>
+        <v>6910007</v>
       </c>
       <c r="B346" s="2" t="n">
         <v>6</v>
@@ -9431,18 +9431,18 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_9</t>
+          <t>Weapon/Weapon_R_7</t>
         </is>
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-铁剑</t>
+          <t>哥布林-武器-死亡之书</t>
         </is>
       </c>
     </row>
     <row r="347" s="3">
       <c r="A347" s="2" t="n">
-        <v>6910010</v>
+        <v>6910008</v>
       </c>
       <c r="B347" s="2" t="n">
         <v>6</v>
@@ -9455,18 +9455,18 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_10</t>
+          <t>Weapon/Weapon_R_8</t>
         </is>
       </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-三叉戟</t>
+          <t>哥布林-武器-猩红之酒</t>
         </is>
       </c>
     </row>
     <row r="348" s="3">
       <c r="A348" s="2" t="n">
-        <v>6910011</v>
+        <v>6910009</v>
       </c>
       <c r="B348" s="2" t="n">
         <v>6</v>
@@ -9479,18 +9479,18 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_11</t>
+          <t>Weapon/Weapon_R_9</t>
         </is>
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-华丽刺剑</t>
+          <t>哥布林-武器-铁剑</t>
         </is>
       </c>
     </row>
     <row r="349" s="3">
       <c r="A349" s="2" t="n">
-        <v>6910012</v>
+        <v>6910010</v>
       </c>
       <c r="B349" s="2" t="n">
         <v>6</v>
@@ -9503,18 +9503,18 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_12</t>
+          <t>Weapon/Weapon_R_10</t>
         </is>
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-拐杖剑</t>
+          <t>哥布林-武器-三叉戟</t>
         </is>
       </c>
     </row>
     <row r="350" s="3">
       <c r="A350" s="2" t="n">
-        <v>6910013</v>
+        <v>6910011</v>
       </c>
       <c r="B350" s="2" t="n">
         <v>6</v>
@@ -9527,18 +9527,18 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_13</t>
+          <t>Weapon/Weapon_R_11</t>
         </is>
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-木铁弓</t>
+          <t>哥布林-武器-华丽刺剑</t>
         </is>
       </c>
     </row>
     <row r="351" s="3">
       <c r="A351" s="2" t="n">
-        <v>6910014</v>
+        <v>6910012</v>
       </c>
       <c r="B351" s="2" t="n">
         <v>6</v>
@@ -9551,18 +9551,18 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_14</t>
+          <t>Weapon/Weapon_R_12</t>
         </is>
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-直弓</t>
+          <t>哥布林-武器-拐杖剑</t>
         </is>
       </c>
     </row>
     <row r="352" s="3">
       <c r="A352" s="2" t="n">
-        <v>6910015</v>
+        <v>6910013</v>
       </c>
       <c r="B352" s="2" t="n">
         <v>6</v>
@@ -9575,18 +9575,18 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_15</t>
+          <t>Weapon/Weapon_R_13</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-魔力弓</t>
+          <t>哥布林-武器-木铁弓</t>
         </is>
       </c>
     </row>
     <row r="353" s="3">
       <c r="A353" s="2" t="n">
-        <v>6910016</v>
+        <v>6910014</v>
       </c>
       <c r="B353" s="2" t="n">
         <v>6</v>
@@ -9599,18 +9599,18 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_16</t>
+          <t>Weapon/Weapon_R_14</t>
         </is>
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-金闪闪弓</t>
+          <t>哥布林-武器-直弓</t>
         </is>
       </c>
     </row>
     <row r="354" s="3">
       <c r="A354" s="2" t="n">
-        <v>6910017</v>
+        <v>6910015</v>
       </c>
       <c r="B354" s="2" t="n">
         <v>6</v>
@@ -9623,18 +9623,18 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_17</t>
+          <t>Weapon/Weapon_R_15</t>
         </is>
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-炸弹</t>
+          <t>哥布林-武器-魔力弓</t>
         </is>
       </c>
     </row>
     <row r="355" s="3">
       <c r="A355" s="2" t="n">
-        <v>6910018</v>
+        <v>6910016</v>
       </c>
       <c r="B355" s="2" t="n">
         <v>6</v>
@@ -9647,18 +9647,18 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_18</t>
+          <t>Weapon/Weapon_R_16</t>
         </is>
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-火药</t>
+          <t>哥布林-武器-金闪闪弓</t>
         </is>
       </c>
     </row>
     <row r="356" s="3">
       <c r="A356" s="2" t="n">
-        <v>6910019</v>
+        <v>6910017</v>
       </c>
       <c r="B356" s="2" t="n">
         <v>6</v>
@@ -9671,18 +9671,18 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_19</t>
+          <t>Weapon/Weapon_R_17</t>
         </is>
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-危险药剂</t>
+          <t>哥布林-武器-炸弹</t>
         </is>
       </c>
     </row>
     <row r="357" s="3">
       <c r="A357" s="2" t="n">
-        <v>6910020</v>
+        <v>6910018</v>
       </c>
       <c r="B357" s="2" t="n">
         <v>6</v>
@@ -9695,66 +9695,66 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_20</t>
+          <t>Weapon/Weapon_R_18</t>
         </is>
       </c>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>哥布林-武器-奥里给</t>
+          <t>哥布林-武器-火药</t>
         </is>
       </c>
     </row>
     <row r="358" s="3">
       <c r="A358" s="2" t="n">
-        <v>7000001</v>
+        <v>6910019</v>
       </c>
       <c r="B358" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C358" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>Base/Base_1</t>
+          <t>Weapon/Weapon_R_19</t>
         </is>
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>兽人-基础</t>
+          <t>哥布林-武器-危险药剂</t>
         </is>
       </c>
     </row>
     <row r="359" s="3">
       <c r="A359" s="2" t="n">
-        <v>7030001</v>
+        <v>6910020</v>
       </c>
       <c r="B359" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C359" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_1</t>
+          <t>Weapon/Weapon_R_20</t>
         </is>
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>发型1</t>
+          <t>哥布林-武器-奥里给</t>
         </is>
       </c>
     </row>
     <row r="360" s="3">
       <c r="A360" s="2" t="n">
-        <v>7030002</v>
+        <v>7000001</v>
       </c>
       <c r="B360" s="2" t="n">
         <v>7</v>
@@ -9763,22 +9763,22 @@
         <v>0</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>Hair/Hair_2</t>
+          <t>Base/Base_1</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>发型2</t>
+          <t>兽人-基础</t>
         </is>
       </c>
     </row>
     <row r="361" s="3">
       <c r="A361" s="2" t="n">
-        <v>7050001</v>
+        <v>7030001</v>
       </c>
       <c r="B361" s="2" t="n">
         <v>7</v>
@@ -9787,22 +9787,22 @@
         <v>0</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_1</t>
+          <t>Hair/Hair_1</t>
         </is>
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>兽人-眼睛-1</t>
+          <t>发型1</t>
         </is>
       </c>
     </row>
     <row r="362" s="3">
       <c r="A362" s="2" t="n">
-        <v>7050002</v>
+        <v>7030002</v>
       </c>
       <c r="B362" s="2" t="n">
         <v>7</v>
@@ -9811,22 +9811,22 @@
         <v>0</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_2</t>
+          <t>Hair/Hair_2</t>
         </is>
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>兽人-眼睛-2</t>
+          <t>发型2</t>
         </is>
       </c>
     </row>
     <row r="363" s="3">
       <c r="A363" s="2" t="n">
-        <v>7050003</v>
+        <v>7050001</v>
       </c>
       <c r="B363" s="2" t="n">
         <v>7</v>
@@ -9839,18 +9839,18 @@
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_3</t>
+          <t>Eye/Eye_1</t>
         </is>
       </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>兽人-眼睛-3</t>
+          <t>兽人-眼睛-1</t>
         </is>
       </c>
     </row>
     <row r="364" s="3">
       <c r="A364" s="2" t="n">
-        <v>7050004</v>
+        <v>7050002</v>
       </c>
       <c r="B364" s="2" t="n">
         <v>7</v>
@@ -9863,18 +9863,18 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_4</t>
+          <t>Eye/Eye_2</t>
         </is>
       </c>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>兽人-眼睛-4</t>
+          <t>兽人-眼睛-2</t>
         </is>
       </c>
     </row>
     <row r="365" s="3">
       <c r="A365" s="2" t="n">
-        <v>7050005</v>
+        <v>7050003</v>
       </c>
       <c r="B365" s="2" t="n">
         <v>7</v>
@@ -9887,18 +9887,18 @@
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>Eye/Eye_5</t>
+          <t>Eye/Eye_3</t>
         </is>
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>兽人-眼睛-5</t>
+          <t>兽人-眼睛-3</t>
         </is>
       </c>
     </row>
     <row r="366" s="3">
       <c r="A366" s="2" t="n">
-        <v>7060001</v>
+        <v>7050004</v>
       </c>
       <c r="B366" s="2" t="n">
         <v>7</v>
@@ -9907,22 +9907,22 @@
         <v>0</v>
       </c>
       <c r="D366" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_1</t>
+          <t>Eye/Eye_4</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-1</t>
+          <t>兽人-眼睛-4</t>
         </is>
       </c>
     </row>
     <row r="367" s="3">
       <c r="A367" s="2" t="n">
-        <v>7060002</v>
+        <v>7050005</v>
       </c>
       <c r="B367" s="2" t="n">
         <v>7</v>
@@ -9931,22 +9931,22 @@
         <v>0</v>
       </c>
       <c r="D367" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_2</t>
+          <t>Eye/Eye_5</t>
         </is>
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-2</t>
+          <t>兽人-眼睛-5</t>
         </is>
       </c>
     </row>
     <row r="368" s="3">
       <c r="A368" s="2" t="n">
-        <v>7060003</v>
+        <v>7060001</v>
       </c>
       <c r="B368" s="2" t="n">
         <v>7</v>
@@ -9959,18 +9959,18 @@
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_3</t>
+          <t>Mouth/Mouth_1</t>
         </is>
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-3</t>
+          <t>嘴巴-1</t>
         </is>
       </c>
     </row>
     <row r="369" s="3">
       <c r="A369" s="2" t="n">
-        <v>7060004</v>
+        <v>7060002</v>
       </c>
       <c r="B369" s="2" t="n">
         <v>7</v>
@@ -9983,18 +9983,18 @@
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_4</t>
+          <t>Mouth/Mouth_2</t>
         </is>
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-4</t>
+          <t>嘴巴-2</t>
         </is>
       </c>
     </row>
     <row r="370" s="3">
       <c r="A370" s="2" t="n">
-        <v>7060005</v>
+        <v>7060003</v>
       </c>
       <c r="B370" s="2" t="n">
         <v>7</v>
@@ -10007,18 +10007,18 @@
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>Mouth/Mouth_5</t>
+          <t>Mouth/Mouth_3</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>嘴巴-5</t>
+          <t>嘴巴-3</t>
         </is>
       </c>
     </row>
     <row r="371" s="3">
       <c r="A371" s="2" t="n">
-        <v>7500001</v>
+        <v>7060004</v>
       </c>
       <c r="B371" s="2" t="n">
         <v>7</v>
@@ -10027,22 +10027,22 @@
         <v>0</v>
       </c>
       <c r="D371" s="2" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>Hat/Hat_1</t>
+          <t>Mouth/Mouth_4</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>兽人帽子-1</t>
+          <t>嘴巴-4</t>
         </is>
       </c>
     </row>
     <row r="372" s="3">
       <c r="A372" s="2" t="n">
-        <v>7510001</v>
+        <v>7060005</v>
       </c>
       <c r="B372" s="2" t="n">
         <v>7</v>
@@ -10051,22 +10051,22 @@
         <v>0</v>
       </c>
       <c r="D372" s="2" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_1</t>
+          <t>Mouth/Mouth_5</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>兽人-衣服-1</t>
+          <t>嘴巴-5</t>
         </is>
       </c>
     </row>
     <row r="373" s="3">
       <c r="A373" s="2" t="n">
-        <v>7510002</v>
+        <v>7500001</v>
       </c>
       <c r="B373" s="2" t="n">
         <v>7</v>
@@ -10075,22 +10075,22 @@
         <v>0</v>
       </c>
       <c r="D373" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>Clothes/Clothes_2</t>
+          <t>Hat/Hat_1</t>
         </is>
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>兽人-衣服-2</t>
+          <t>兽人帽子-1</t>
         </is>
       </c>
     </row>
     <row r="374" s="3">
       <c r="A374" s="2" t="n">
-        <v>7520001</v>
+        <v>7510001</v>
       </c>
       <c r="B374" s="2" t="n">
         <v>7</v>
@@ -10099,22 +10099,22 @@
         <v>0</v>
       </c>
       <c r="D374" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_1</t>
+          <t>Clothes/Clothes_1</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>裤子1</t>
+          <t>兽人-衣服-1</t>
         </is>
       </c>
     </row>
     <row r="375" s="3">
       <c r="A375" s="2" t="n">
-        <v>7520002</v>
+        <v>7510002</v>
       </c>
       <c r="B375" s="2" t="n">
         <v>7</v>
@@ -10123,22 +10123,22 @@
         <v>0</v>
       </c>
       <c r="D375" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_2</t>
+          <t>Clothes/Clothes_2</t>
         </is>
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>裤子2</t>
+          <t>兽人-衣服-2</t>
         </is>
       </c>
     </row>
     <row r="376" s="3">
       <c r="A376" s="2" t="n">
-        <v>7520003</v>
+        <v>7520001</v>
       </c>
       <c r="B376" s="2" t="n">
         <v>7</v>
@@ -10151,18 +10151,18 @@
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_3</t>
+          <t>Pants/Pants_1</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>裤子3</t>
+          <t>裤子1</t>
         </is>
       </c>
     </row>
     <row r="377" s="3">
       <c r="A377" s="2" t="n">
-        <v>7520004</v>
+        <v>7520002</v>
       </c>
       <c r="B377" s="2" t="n">
         <v>7</v>
@@ -10175,18 +10175,18 @@
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>Pants/Pants_4</t>
+          <t>Pants/Pants_2</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>裤子4</t>
+          <t>裤子2</t>
         </is>
       </c>
     </row>
     <row r="378" s="3">
       <c r="A378" s="2" t="n">
-        <v>7900001</v>
+        <v>7520003</v>
       </c>
       <c r="B378" s="2" t="n">
         <v>7</v>
@@ -10195,22 +10195,22 @@
         <v>0</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_1</t>
+          <t>Pants/Pants_3</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>兽人-武器-左-1</t>
+          <t>裤子3</t>
         </is>
       </c>
     </row>
     <row r="379" s="3">
       <c r="A379" s="2" t="n">
-        <v>7900002</v>
+        <v>7520004</v>
       </c>
       <c r="B379" s="2" t="n">
         <v>7</v>
@@ -10219,22 +10219,22 @@
         <v>0</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_2</t>
+          <t>Pants/Pants_4</t>
         </is>
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>兽人-武器-左-2</t>
+          <t>裤子4</t>
         </is>
       </c>
     </row>
     <row r="380" ht="12" customHeight="1" s="3">
       <c r="A380" s="2" t="n">
-        <v>7900003</v>
+        <v>7900001</v>
       </c>
       <c r="B380" s="2" t="n">
         <v>7</v>
@@ -10247,18 +10247,18 @@
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_L_3</t>
+          <t>Weapon/Weapon_L_1</t>
         </is>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>兽人-武器-左-3</t>
+          <t>兽人-武器-左-1</t>
         </is>
       </c>
     </row>
     <row r="381" s="3">
       <c r="A381" s="2" t="n">
-        <v>7910001</v>
+        <v>7900002</v>
       </c>
       <c r="B381" s="2" t="n">
         <v>7</v>
@@ -10267,22 +10267,22 @@
         <v>0</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_1</t>
+          <t>Weapon/Weapon_L_2</t>
         </is>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>兽人-武器-右-1</t>
+          <t>兽人-武器-左-2</t>
         </is>
       </c>
     </row>
     <row r="382" s="3">
       <c r="A382" s="2" t="n">
-        <v>7910002</v>
+        <v>7900003</v>
       </c>
       <c r="B382" s="2" t="n">
         <v>7</v>
@@ -10291,22 +10291,22 @@
         <v>0</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_2</t>
+          <t>Weapon/Weapon_L_3</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>兽人-武器-右-2</t>
+          <t>兽人-武器-左-3</t>
         </is>
       </c>
     </row>
     <row r="383" s="3">
       <c r="A383" s="2" t="n">
-        <v>7910003</v>
+        <v>7910001</v>
       </c>
       <c r="B383" s="2" t="n">
         <v>7</v>
@@ -10319,18 +10319,18 @@
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_3</t>
+          <t>Weapon/Weapon_R_1</t>
         </is>
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>兽人-武器-右-3</t>
+          <t>兽人-武器-右-1</t>
         </is>
       </c>
     </row>
     <row r="384" s="3">
       <c r="A384" s="2" t="n">
-        <v>7910004</v>
+        <v>7910002</v>
       </c>
       <c r="B384" s="2" t="n">
         <v>7</v>
@@ -10343,18 +10343,18 @@
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_4</t>
+          <t>Weapon/Weapon_R_2</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>兽人-武器-右-4</t>
+          <t>兽人-武器-右-2</t>
         </is>
       </c>
     </row>
     <row r="385" s="3">
       <c r="A385" s="2" t="n">
-        <v>7910005</v>
+        <v>7910003</v>
       </c>
       <c r="B385" s="2" t="n">
         <v>7</v>
@@ -10367,18 +10367,18 @@
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_5</t>
+          <t>Weapon/Weapon_R_3</t>
         </is>
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>兽人-武器-右-5</t>
+          <t>兽人-武器-右-3</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>7910006</v>
+        <v>7910004</v>
       </c>
       <c r="B386" s="2" t="n">
         <v>7</v>
@@ -10391,56 +10391,66 @@
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>Weapon/Weapon_R_6</t>
+          <t>Weapon/Weapon_R_4</t>
         </is>
       </c>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>兽人-武器-右-6</t>
+          <t>兽人-武器-右-4</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>99995005001</v>
+        <v>7910005</v>
       </c>
       <c r="B387" s="2" t="n">
-        <v>999950</v>
+        <v>7</v>
       </c>
       <c r="C387" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>fennu</t>
+          <t>Weapon/Weapon_R_5</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>兽人-武器-右-5</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>99995005002</v>
+        <v>7910006</v>
       </c>
       <c r="B388" s="2" t="n">
-        <v>999950</v>
+        <v>7</v>
       </c>
       <c r="C388" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>jinghuang</t>
+          <t>Weapon/Weapon_R_6</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>兽人-武器-右-6</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>99995005003</v>
+        <v>99995005001</v>
       </c>
       <c r="B389" s="2" t="n">
         <v>999950</v>
@@ -10453,13 +10463,13 @@
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>kaixin</t>
+          <t>fennu</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>99995005004</v>
+        <v>99995005002</v>
       </c>
       <c r="B390" s="2" t="n">
         <v>999950</v>
@@ -10472,13 +10482,13 @@
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>ku</t>
+          <t>jinghuang</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>99995005005</v>
+        <v>99995005003</v>
       </c>
       <c r="B391" s="2" t="n">
         <v>999950</v>
@@ -10491,16 +10501,16 @@
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>kaixin</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>99994705001</v>
+        <v>99995005004</v>
       </c>
       <c r="B392" s="2" t="n">
-        <v>999947</v>
+        <v>999950</v>
       </c>
       <c r="C392" s="2" t="n">
         <v>1</v>
@@ -10510,16 +10520,16 @@
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>ku</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>99994705002</v>
+        <v>99995005005</v>
       </c>
       <c r="B393" s="2" t="n">
-        <v>999947</v>
+        <v>999950</v>
       </c>
       <c r="C393" s="2" t="n">
         <v>1</v>
@@ -10529,13 +10539,13 @@
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>wait</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>99994705003</v>
+        <v>99994705001</v>
       </c>
       <c r="B394" s="2" t="n">
         <v>999947</v>
@@ -10548,13 +10558,13 @@
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>angry</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>99994705004</v>
+        <v>99994705002</v>
       </c>
       <c r="B395" s="2" t="n">
         <v>999947</v>
@@ -10567,16 +10577,16 @@
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>happy</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>99996105001</v>
+        <v>99994705003</v>
       </c>
       <c r="B396" s="2" t="n">
-        <v>999961</v>
+        <v>999947</v>
       </c>
       <c r="C396" s="2" t="n">
         <v>1</v>
@@ -10586,16 +10596,16 @@
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>fennu</t>
+          <t>sad</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>99996105002</v>
+        <v>99994705004</v>
       </c>
       <c r="B397" s="2" t="n">
-        <v>999961</v>
+        <v>999947</v>
       </c>
       <c r="C397" s="2" t="n">
         <v>1</v>
@@ -10605,13 +10615,13 @@
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>haixiu</t>
+          <t>wait</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>99996105003</v>
+        <v>99996105001</v>
       </c>
       <c r="B398" s="2" t="n">
         <v>999961</v>
@@ -10624,13 +10634,13 @@
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>jingya</t>
+          <t>fennu</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>99996105004</v>
+        <v>99996105002</v>
       </c>
       <c r="B399" s="2" t="n">
         <v>999961</v>
@@ -10643,13 +10653,13 @@
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>haixiu</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>99996105005</v>
+        <v>99996105003</v>
       </c>
       <c r="B400" s="2" t="n">
         <v>999961</v>
@@ -10662,16 +10672,16 @@
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>xiao</t>
+          <t>jingya</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>99996805001</v>
+        <v>99996105004</v>
       </c>
       <c r="B401" s="2" t="n">
-        <v>999968</v>
+        <v>999961</v>
       </c>
       <c r="C401" s="2" t="n">
         <v>1</v>
@@ -10681,16 +10691,16 @@
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>wait</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>99996805002</v>
+        <v>99996105005</v>
       </c>
       <c r="B402" s="2" t="n">
-        <v>999968</v>
+        <v>999961</v>
       </c>
       <c r="C402" s="2" t="n">
         <v>1</v>
@@ -10700,13 +10710,13 @@
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>blinky</t>
+          <t>xiao</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>99996805003</v>
+        <v>99996805001</v>
       </c>
       <c r="B403" s="2" t="n">
         <v>999968</v>
@@ -10719,13 +10729,13 @@
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>sleepy</t>
+          <t>angry</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>99996805004</v>
+        <v>99996805002</v>
       </c>
       <c r="B404" s="2" t="n">
         <v>999968</v>
@@ -10738,16 +10748,16 @@
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>blinky</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>99997905001</v>
+        <v>99996805003</v>
       </c>
       <c r="B405" s="2" t="n">
-        <v>999979</v>
+        <v>999968</v>
       </c>
       <c r="C405" s="2" t="n">
         <v>1</v>
@@ -10757,16 +10767,16 @@
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>sleepy</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>99997905002</v>
+        <v>99996805004</v>
       </c>
       <c r="B406" s="2" t="n">
-        <v>999979</v>
+        <v>999968</v>
       </c>
       <c r="C406" s="2" t="n">
         <v>1</v>
@@ -10776,13 +10786,13 @@
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>Relax</t>
+          <t>wait</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>99997905003</v>
+        <v>99997905001</v>
       </c>
       <c r="B407" s="2" t="n">
         <v>999979</v>
@@ -10795,13 +10805,13 @@
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>anran</t>
+          <t>Pain</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>99997905004</v>
+        <v>99997905002</v>
       </c>
       <c r="B408" s="2" t="n">
         <v>999979</v>
@@ -10814,13 +10824,13 @@
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>biyan</t>
+          <t>Relax</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>99997905005</v>
+        <v>99997905003</v>
       </c>
       <c r="B409" s="2" t="n">
         <v>999979</v>
@@ -10833,16 +10843,16 @@
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>anran</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>99997405001</v>
+        <v>99997905004</v>
       </c>
       <c r="B410" s="2" t="n">
-        <v>999974</v>
+        <v>999979</v>
       </c>
       <c r="C410" s="2" t="n">
         <v>1</v>
@@ -10858,10 +10868,10 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>99997405002</v>
+        <v>99997905005</v>
       </c>
       <c r="B411" s="2" t="n">
-        <v>999974</v>
+        <v>999979</v>
       </c>
       <c r="C411" s="2" t="n">
         <v>1</v>
@@ -10871,13 +10881,13 @@
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>fennu</t>
+          <t>wait</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>99997405003</v>
+        <v>99997405001</v>
       </c>
       <c r="B412" s="2" t="n">
         <v>999974</v>
@@ -10890,13 +10900,13 @@
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>biyan</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>99997405004</v>
+        <v>99997405002</v>
       </c>
       <c r="B413" s="2" t="n">
         <v>999974</v>
@@ -10909,16 +10919,16 @@
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>weixiao</t>
+          <t>fennu</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>99998605001</v>
+        <v>99997405003</v>
       </c>
       <c r="B414" s="2" t="n">
-        <v>999986</v>
+        <v>999974</v>
       </c>
       <c r="C414" s="2" t="n">
         <v>1</v>
@@ -10928,16 +10938,16 @@
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>Beishang</t>
+          <t>wait</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>99998605002</v>
+        <v>99997405004</v>
       </c>
       <c r="B415" s="2" t="n">
-        <v>999986</v>
+        <v>999974</v>
       </c>
       <c r="C415" s="2" t="n">
         <v>1</v>
@@ -10947,13 +10957,13 @@
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>Shengqi</t>
+          <t>weixiao</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>99998605003</v>
+        <v>99998605001</v>
       </c>
       <c r="B416" s="2" t="n">
         <v>999986</v>
@@ -10966,13 +10976,13 @@
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>Smile</t>
+          <t>Beishang</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>99998605004</v>
+        <v>99998605002</v>
       </c>
       <c r="B417" s="2" t="n">
         <v>999986</v>
@@ -10985,16 +10995,16 @@
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>Wait</t>
+          <t>Shengqi</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>99998705001</v>
+        <v>99998605003</v>
       </c>
       <c r="B418" s="2" t="n">
-        <v>999987</v>
+        <v>999986</v>
       </c>
       <c r="C418" s="2" t="n">
         <v>1</v>
@@ -11004,16 +11014,16 @@
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>Smile</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>99998705002</v>
+        <v>99998605004</v>
       </c>
       <c r="B419" s="2" t="n">
-        <v>999987</v>
+        <v>999986</v>
       </c>
       <c r="C419" s="2" t="n">
         <v>1</v>
@@ -11023,13 +11033,13 @@
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>Wait</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>99998705003</v>
+        <v>99998705001</v>
       </c>
       <c r="B420" s="2" t="n">
         <v>999987</v>
@@ -11042,13 +11052,13 @@
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>exciting</t>
+          <t>angry</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>99998705004</v>
+        <v>99998705002</v>
       </c>
       <c r="B421" s="2" t="n">
         <v>999987</v>
@@ -11061,16 +11071,16 @@
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>calm</t>
         </is>
       </c>
     </row>
     <row r="422" ht="12" customHeight="1" s="3">
       <c r="A422" s="2" t="n">
-        <v>99998705005</v>
+        <v>99998705003</v>
       </c>
       <c r="B422" s="2" t="n">
-        <v>999988</v>
+        <v>999987</v>
       </c>
       <c r="C422" s="2" t="n">
         <v>1</v>
@@ -11080,16 +11090,16 @@
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>exciting</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>99998905001</v>
+        <v>99998705004</v>
       </c>
       <c r="B423" s="2" t="n">
-        <v>999989</v>
+        <v>999987</v>
       </c>
       <c r="C423" s="2" t="n">
         <v>1</v>
@@ -11099,16 +11109,16 @@
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>sad</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>99998905002</v>
+        <v>99998705005</v>
       </c>
       <c r="B424" s="2" t="n">
-        <v>999989</v>
+        <v>999988</v>
       </c>
       <c r="C424" s="2" t="n">
         <v>1</v>
@@ -11118,13 +11128,13 @@
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>wait</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>99998905003</v>
+        <v>99998905001</v>
       </c>
       <c r="B425" s="2" t="n">
         <v>999989</v>
@@ -11137,13 +11147,13 @@
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>Wait</t>
+          <t>Angry</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>99998905004</v>
+        <v>99998905002</v>
       </c>
       <c r="B426" s="2" t="n">
         <v>999989</v>
@@ -11156,16 +11166,16 @@
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>Xiao</t>
+          <t>Sad</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>99999505001</v>
+        <v>99998905003</v>
       </c>
       <c r="B427" s="2" t="n">
-        <v>999995</v>
+        <v>999989</v>
       </c>
       <c r="C427" s="2" t="n">
         <v>1</v>
@@ -11175,16 +11185,16 @@
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>biyan</t>
+          <t>Wait</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>99999505002</v>
+        <v>99998905004</v>
       </c>
       <c r="B428" s="2" t="n">
-        <v>999995</v>
+        <v>999989</v>
       </c>
       <c r="C428" s="2" t="n">
         <v>1</v>
@@ -11194,13 +11204,13 @@
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>fankun</t>
+          <t>Xiao</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>99999505003</v>
+        <v>99999505001</v>
       </c>
       <c r="B429" s="2" t="n">
         <v>999995</v>
@@ -11213,13 +11223,13 @@
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>haoqi</t>
+          <t>biyan</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>99999505004</v>
+        <v>99999505002</v>
       </c>
       <c r="B430" s="2" t="n">
         <v>999995</v>
@@ -11232,13 +11242,13 @@
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>fankun</t>
         </is>
       </c>
     </row>
     <row r="431" ht="15" customHeight="1" s="3">
       <c r="A431" s="2" t="n">
-        <v>99999505005</v>
+        <v>99999505003</v>
       </c>
       <c r="B431" s="2" t="n">
         <v>999995</v>
@@ -11251,16 +11261,16 @@
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>weixiao</t>
+          <t>haoqi</t>
         </is>
       </c>
     </row>
     <row r="432" ht="15" customHeight="1" s="3">
       <c r="A432" s="2" t="n">
-        <v>99999605001</v>
+        <v>99999505004</v>
       </c>
       <c r="B432" s="2" t="n">
-        <v>999996</v>
+        <v>999995</v>
       </c>
       <c r="C432" s="2" t="n">
         <v>1</v>
@@ -11270,16 +11280,16 @@
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>wait</t>
         </is>
       </c>
     </row>
     <row r="433" ht="15" customHeight="1" s="3">
       <c r="A433" s="2" t="n">
-        <v>99999605002</v>
+        <v>99999505005</v>
       </c>
       <c r="B433" s="2" t="n">
-        <v>999996</v>
+        <v>999995</v>
       </c>
       <c r="C433" s="2" t="n">
         <v>1</v>
@@ -11289,13 +11299,13 @@
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>weixiao</t>
         </is>
       </c>
     </row>
     <row r="434" ht="15" customHeight="1" s="3">
       <c r="A434" s="2" t="n">
-        <v>99999605003</v>
+        <v>99999605001</v>
       </c>
       <c r="B434" s="2" t="n">
         <v>999996</v>
@@ -11308,13 +11318,13 @@
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>angry</t>
         </is>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1" s="3">
       <c r="A435" s="2" t="n">
-        <v>99999605004</v>
+        <v>99999605002</v>
       </c>
       <c r="B435" s="2" t="n">
         <v>999996</v>
@@ -11327,13 +11337,13 @@
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>happy</t>
         </is>
       </c>
     </row>
     <row r="436" ht="15" customHeight="1" s="3">
       <c r="A436" s="2" t="n">
-        <v>99999605005</v>
+        <v>99999605003</v>
       </c>
       <c r="B436" s="2" t="n">
         <v>999996</v>
@@ -11346,16 +11356,16 @@
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>sad</t>
         </is>
       </c>
     </row>
     <row r="437" ht="15" customHeight="1" s="3">
       <c r="A437" s="2" t="n">
-        <v>99999905001</v>
+        <v>99999605004</v>
       </c>
       <c r="B437" s="2" t="n">
-        <v>999999</v>
+        <v>999996</v>
       </c>
       <c r="C437" s="2" t="n">
         <v>1</v>
@@ -11365,16 +11375,16 @@
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>jingya</t>
+          <t>surprised</t>
         </is>
       </c>
     </row>
     <row r="438" ht="15" customHeight="1" s="3">
       <c r="A438" s="2" t="n">
-        <v>99999905002</v>
+        <v>99999605005</v>
       </c>
       <c r="B438" s="2" t="n">
-        <v>999999</v>
+        <v>999996</v>
       </c>
       <c r="C438" s="2" t="n">
         <v>1</v>
@@ -11390,7 +11400,7 @@
     </row>
     <row r="439" ht="15" customHeight="1" s="3">
       <c r="A439" s="2" t="n">
-        <v>99999905003</v>
+        <v>99999905001</v>
       </c>
       <c r="B439" s="2" t="n">
         <v>999999</v>
@@ -11403,13 +11413,13 @@
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>weixiao</t>
+          <t>jingya</t>
         </is>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1" s="3">
       <c r="A440" s="2" t="n">
-        <v>99999905004</v>
+        <v>99999905002</v>
       </c>
       <c r="B440" s="2" t="n">
         <v>999999</v>
@@ -11422,13 +11432,13 @@
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>yansu</t>
+          <t>wait</t>
         </is>
       </c>
     </row>
     <row r="441" ht="15" customHeight="1" s="3">
       <c r="A441" s="2" t="n">
-        <v>99999905005</v>
+        <v>99999905003</v>
       </c>
       <c r="B441" s="2" t="n">
         <v>999999</v>
@@ -11440,6 +11450,44 @@
         <v>5</v>
       </c>
       <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>weixiao</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="n">
+        <v>99999905004</v>
+      </c>
+      <c r="B442" s="2" t="n">
+        <v>999999</v>
+      </c>
+      <c r="C442" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D442" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>yansu</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n">
+        <v>99999905005</v>
+      </c>
+      <c r="B443" s="2" t="n">
+        <v>999999</v>
+      </c>
+      <c r="C443" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D443" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
         <is>
           <t>yaoya</t>
         </is>
